--- a/app/static/bah_2025.xlsx
+++ b/app/static/bah_2025.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CCF494-AE0C-40E9-A2AF-844B46BCB1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA4EEE2-1DBD-45F7-9337-19BEB36BA74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="With" sheetId="1" r:id="rId1"/>
-    <sheet name="Without" sheetId="2" r:id="rId2"/>
+    <sheet name="with" sheetId="1" r:id="rId1"/>
+    <sheet name="without" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">With!$A$1:$Z$338</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Without!$A$1:$Z$337</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">With!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">Without!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">with!$A$1:$Z$338</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">without!$A$1:$Z$337</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">with!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">without!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,78 +40,6 @@
     <t>MHA</t>
   </si>
   <si>
-    <t>E01</t>
-  </si>
-  <si>
-    <t>E02</t>
-  </si>
-  <si>
-    <t>E03</t>
-  </si>
-  <si>
-    <t>E04</t>
-  </si>
-  <si>
-    <t>E05</t>
-  </si>
-  <si>
-    <t>E06</t>
-  </si>
-  <si>
-    <t>E07</t>
-  </si>
-  <si>
-    <t>E08</t>
-  </si>
-  <si>
-    <t>E09</t>
-  </si>
-  <si>
-    <t>W01</t>
-  </si>
-  <si>
-    <t>W02</t>
-  </si>
-  <si>
-    <t>W03</t>
-  </si>
-  <si>
-    <t>W04</t>
-  </si>
-  <si>
-    <t>W05</t>
-  </si>
-  <si>
-    <t>O01E</t>
-  </si>
-  <si>
-    <t>O02E</t>
-  </si>
-  <si>
-    <t>O03E</t>
-  </si>
-  <si>
-    <t>O01</t>
-  </si>
-  <si>
-    <t>O02</t>
-  </si>
-  <si>
-    <t>O03</t>
-  </si>
-  <si>
-    <t>O04</t>
-  </si>
-  <si>
-    <t>O05</t>
-  </si>
-  <si>
-    <t>O06</t>
-  </si>
-  <si>
-    <t>O07</t>
-  </si>
-  <si>
     <t>MHA_NAME</t>
   </si>
   <si>
@@ -2141,6 +2069,78 @@
   </si>
   <si>
     <t>DAHLGREN/FORT WALKER, VA</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>W1</t>
+  </si>
+  <si>
+    <t>W2</t>
+  </si>
+  <si>
+    <t>W3</t>
+  </si>
+  <si>
+    <t>W4</t>
+  </si>
+  <si>
+    <t>W5</t>
+  </si>
+  <si>
+    <t>O1E</t>
+  </si>
+  <si>
+    <t>O2E</t>
+  </si>
+  <si>
+    <t>O3E</t>
+  </si>
+  <si>
+    <t>O1</t>
+  </si>
+  <si>
+    <t>O2</t>
+  </si>
+  <si>
+    <t>O3</t>
+  </si>
+  <si>
+    <t>O4</t>
+  </si>
+  <si>
+    <t>O5</t>
+  </si>
+  <si>
+    <t>O6</t>
+  </si>
+  <si>
+    <t>O7</t>
   </si>
 </sst>
 </file>
@@ -2203,27 +2203,27 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2556,89 +2556,89 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>24</v>
+      <c r="C1" s="7" t="s">
+        <v>678</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>681</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>684</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>685</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>689</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>690</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>699</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>701</v>
       </c>
       <c r="AA1" s="3"/>
       <c r="AD1" s="2"/>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6">
         <v>2331</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6">
         <v>2091</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C4" s="6">
         <v>2319</v>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6">
         <v>2268</v>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C6" s="6">
         <v>2229</v>
@@ -3045,10 +3045,10 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C7" s="6">
         <v>1995</v>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6">
         <v>1113</v>
@@ -3209,10 +3209,10 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="C9" s="6">
         <v>1392</v>
@@ -3291,10 +3291,10 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C10" s="6">
         <v>1698</v>
@@ -3373,10 +3373,10 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C11" s="6">
         <v>1698</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C12" s="6">
         <v>1548</v>
@@ -3537,10 +3537,10 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C13" s="6">
         <v>1527</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C14" s="6">
         <v>1923</v>
@@ -3701,10 +3701,10 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C15" s="6">
         <v>1686</v>
@@ -3783,10 +3783,10 @@
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C16" s="6">
         <v>1122</v>
@@ -3865,10 +3865,10 @@
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C17" s="6">
         <v>1551</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C18" s="6">
         <v>2163</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C19" s="6">
         <v>1578</v>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C20" s="6">
         <v>1689</v>
@@ -4193,10 +4193,10 @@
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C21" s="6">
         <v>1557</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C22" s="6">
         <v>3393</v>
@@ -4357,10 +4357,10 @@
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C23" s="6">
         <v>4596</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C24" s="6">
         <v>1425</v>
@@ -4521,10 +4521,10 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C25" s="6">
         <v>2139</v>
@@ -4603,10 +4603,10 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C26" s="6">
         <v>1926</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C27" s="6">
         <v>3594</v>
@@ -4767,10 +4767,10 @@
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C28" s="6">
         <v>3396</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C29" s="6">
         <v>3048</v>
@@ -4931,10 +4931,10 @@
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C30" s="6">
         <v>3114</v>
@@ -5013,10 +5013,10 @@
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C31" s="6">
         <v>1842</v>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C32" s="6">
         <v>2922</v>
@@ -5177,10 +5177,10 @@
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C33" s="6">
         <v>1941</v>
@@ -5259,10 +5259,10 @@
     </row>
     <row r="34" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C34" s="6">
         <v>2787</v>
@@ -5341,10 +5341,10 @@
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C35" s="6">
         <v>2592</v>
@@ -5423,10 +5423,10 @@
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C36" s="6">
         <v>2337</v>
@@ -5505,10 +5505,10 @@
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C37" s="6">
         <v>3042</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C38" s="6">
         <v>3459</v>
@@ -5669,10 +5669,10 @@
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C39" s="6">
         <v>3663</v>
@@ -5751,10 +5751,10 @@
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C40" s="6">
         <v>3114</v>
@@ -5833,10 +5833,10 @@
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C41" s="6">
         <v>3042</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C42" s="6">
         <v>1617</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="43" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C43" s="6">
         <v>4155</v>
@@ -6079,10 +6079,10 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C44" s="6">
         <v>2865</v>
@@ -6161,10 +6161,10 @@
     </row>
     <row r="45" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C45" s="6">
         <v>1950</v>
@@ -6243,10 +6243,10 @@
     </row>
     <row r="46" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C46" s="6">
         <v>1920</v>
@@ -6325,10 +6325,10 @@
     </row>
     <row r="47" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A47" s="6" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C47" s="6">
         <v>2403</v>
@@ -6407,10 +6407,10 @@
     </row>
     <row r="48" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C48" s="6">
         <v>2580</v>
@@ -6489,10 +6489,10 @@
     </row>
     <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C49" s="6">
         <v>2160</v>
@@ -6571,10 +6571,10 @@
     </row>
     <row r="50" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C50" s="6">
         <v>2013</v>
@@ -6653,10 +6653,10 @@
     </row>
     <row r="51" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C51" s="6">
         <v>2463</v>
@@ -6735,10 +6735,10 @@
     </row>
     <row r="52" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C52" s="6">
         <v>2265</v>
@@ -6817,10 +6817,10 @@
     </row>
     <row r="53" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C53" s="6">
         <v>2448</v>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="54" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="C54" s="6">
         <v>2961</v>
@@ -6981,10 +6981,10 @@
     </row>
     <row r="55" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="C55" s="6">
         <v>2922</v>
@@ -7063,10 +7063,10 @@
     </row>
     <row r="56" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C56" s="6">
         <v>2163</v>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="57" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C57" s="6">
         <v>2247</v>
@@ -7227,10 +7227,10 @@
     </row>
     <row r="58" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A58" s="6" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C58" s="6">
         <v>1947</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="59" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C59" s="6">
         <v>2100</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="60" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C60" s="6">
         <v>2253</v>
@@ -7473,10 +7473,10 @@
     </row>
     <row r="61" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C61" s="6">
         <v>3288</v>
@@ -7555,10 +7555,10 @@
     </row>
     <row r="62" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C62" s="6">
         <v>2394</v>
@@ -7637,10 +7637,10 @@
     </row>
     <row r="63" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A63" s="6" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C63" s="6">
         <v>2064</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="64" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A64" s="6" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C64" s="6">
         <v>1773</v>
@@ -7801,10 +7801,10 @@
     </row>
     <row r="65" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A65" s="6" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="C65" s="6">
         <v>1647</v>
@@ -7883,10 +7883,10 @@
     </row>
     <row r="66" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A66" s="6" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C66" s="6">
         <v>2523</v>
@@ -7965,10 +7965,10 @@
     </row>
     <row r="67" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A67" s="6" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C67" s="6">
         <v>3105</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="68" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A68" s="6" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C68" s="6">
         <v>2121</v>
@@ -8129,10 +8129,10 @@
     </row>
     <row r="69" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C69" s="6">
         <v>3735</v>
@@ -8211,10 +8211,10 @@
     </row>
     <row r="70" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A70" s="6" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C70" s="6">
         <v>2118</v>
@@ -8293,10 +8293,10 @@
     </row>
     <row r="71" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C71" s="6">
         <v>2388</v>
@@ -8375,10 +8375,10 @@
     </row>
     <row r="72" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C72" s="6">
         <v>2610</v>
@@ -8457,10 +8457,10 @@
     </row>
     <row r="73" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A73" s="6" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C73" s="6">
         <v>2247</v>
@@ -8539,10 +8539,10 @@
     </row>
     <row r="74" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A74" s="6" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C74" s="6">
         <v>1296</v>
@@ -8621,10 +8621,10 @@
     </row>
     <row r="75" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A75" s="6" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="C75" s="6">
         <v>1719</v>
@@ -8703,10 +8703,10 @@
     </row>
     <row r="76" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A76" s="6" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C76" s="6">
         <v>2013</v>
@@ -8785,10 +8785,10 @@
     </row>
     <row r="77" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A77" s="6" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="C77" s="6">
         <v>1590</v>
@@ -8867,10 +8867,10 @@
     </row>
     <row r="78" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A78" s="6" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C78" s="6">
         <v>1683</v>
@@ -8949,10 +8949,10 @@
     </row>
     <row r="79" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A79" s="6" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C79" s="6">
         <v>2181</v>
@@ -9031,10 +9031,10 @@
     </row>
     <row r="80" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A80" s="6" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C80" s="6">
         <v>2043</v>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="81" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A81" s="6" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C81" s="6">
         <v>2040</v>
@@ -9195,10 +9195,10 @@
     </row>
     <row r="82" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A82" s="6" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C82" s="6">
         <v>1392</v>
@@ -9277,10 +9277,10 @@
     </row>
     <row r="83" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A83" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C83" s="6">
         <v>3783</v>
@@ -9359,10 +9359,10 @@
     </row>
     <row r="84" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A84" s="6" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C84" s="6">
         <v>3204</v>
@@ -9441,10 +9441,10 @@
     </row>
     <row r="85" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A85" s="6" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C85" s="6">
         <v>3273</v>
@@ -9523,10 +9523,10 @@
     </row>
     <row r="86" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A86" s="6" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="C86" s="6">
         <v>3357</v>
@@ -9605,10 +9605,10 @@
     </row>
     <row r="87" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C87" s="6">
         <v>1425</v>
@@ -9687,10 +9687,10 @@
     </row>
     <row r="88" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A88" s="6" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C88" s="6">
         <v>1938</v>
@@ -9769,10 +9769,10 @@
     </row>
     <row r="89" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A89" s="6" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C89" s="6">
         <v>1593</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="90" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A90" s="6" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C90" s="6">
         <v>1341</v>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="91" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A91" s="6" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C91" s="6">
         <v>1515</v>
@@ -10015,10 +10015,10 @@
     </row>
     <row r="92" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A92" s="6" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C92" s="6">
         <v>1371</v>
@@ -10097,10 +10097,10 @@
     </row>
     <row r="93" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A93" s="6" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C93" s="6">
         <v>2082</v>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="94" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A94" s="6" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C94" s="6">
         <v>1458</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="95" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A95" s="6" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C95" s="6">
         <v>2901</v>
@@ -10343,10 +10343,10 @@
     </row>
     <row r="96" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A96" s="6" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="C96" s="6">
         <v>1368</v>
@@ -10425,10 +10425,10 @@
     </row>
     <row r="97" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A97" s="6" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C97" s="6">
         <v>1716</v>
@@ -10507,10 +10507,10 @@
     </row>
     <row r="98" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A98" s="6" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C98" s="6">
         <v>1668</v>
@@ -10589,10 +10589,10 @@
     </row>
     <row r="99" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A99" s="6" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C99" s="6">
         <v>1314</v>
@@ -10671,10 +10671,10 @@
     </row>
     <row r="100" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A100" s="6" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C100" s="6">
         <v>1647</v>
@@ -10753,10 +10753,10 @@
     </row>
     <row r="101" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A101" s="6" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="C101" s="6">
         <v>1206</v>
@@ -10835,10 +10835,10 @@
     </row>
     <row r="102" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A102" s="6" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C102" s="6">
         <v>1254</v>
@@ -10917,10 +10917,10 @@
     </row>
     <row r="103" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A103" s="6" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C103" s="6">
         <v>1680</v>
@@ -10999,10 +10999,10 @@
     </row>
     <row r="104" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A104" s="6" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C104" s="6">
         <v>1353</v>
@@ -11081,10 +11081,10 @@
     </row>
     <row r="105" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A105" s="6" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C105" s="6">
         <v>1773</v>
@@ -11163,10 +11163,10 @@
     </row>
     <row r="106" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A106" s="6" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C106" s="6">
         <v>1614</v>
@@ -11245,10 +11245,10 @@
     </row>
     <row r="107" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A107" s="6" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C107" s="6">
         <v>1773</v>
@@ -11327,10 +11327,10 @@
     </row>
     <row r="108" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A108" s="6" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C108" s="6">
         <v>1452</v>
@@ -11409,10 +11409,10 @@
     </row>
     <row r="109" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A109" s="6" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C109" s="6">
         <v>1167</v>
@@ -11491,10 +11491,10 @@
     </row>
     <row r="110" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C110" s="6">
         <v>1269</v>
@@ -11573,10 +11573,10 @@
     </row>
     <row r="111" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A111" s="6" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="C111" s="6">
         <v>1182</v>
@@ -11655,10 +11655,10 @@
     </row>
     <row r="112" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A112" s="6" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C112" s="6">
         <v>1728</v>
@@ -11737,10 +11737,10 @@
     </row>
     <row r="113" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A113" s="6" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>693</v>
+        <v>669</v>
       </c>
       <c r="C113" s="6">
         <v>1131</v>
@@ -11819,10 +11819,10 @@
     </row>
     <row r="114" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A114" s="6" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C114" s="6">
         <v>1725</v>
@@ -11901,10 +11901,10 @@
     </row>
     <row r="115" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A115" s="6" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C115" s="6">
         <v>1545</v>
@@ -11983,10 +11983,10 @@
     </row>
     <row r="116" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A116" s="6" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C116" s="6">
         <v>1530</v>
@@ -12065,10 +12065,10 @@
     </row>
     <row r="117" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A117" s="6" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="C117" s="6">
         <v>1509</v>
@@ -12147,10 +12147,10 @@
     </row>
     <row r="118" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A118" s="6" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C118" s="6">
         <v>1254</v>
@@ -12229,10 +12229,10 @@
     </row>
     <row r="119" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C119" s="6">
         <v>1104</v>
@@ -12311,10 +12311,10 @@
     </row>
     <row r="120" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="C120" s="6">
         <v>3900</v>
@@ -12393,10 +12393,10 @@
     </row>
     <row r="121" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C121" s="6">
         <v>4194</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="122" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C122" s="6">
         <v>2739</v>
@@ -12557,10 +12557,10 @@
     </row>
     <row r="123" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C123" s="6">
         <v>2961</v>
@@ -12639,10 +12639,10 @@
     </row>
     <row r="124" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C124" s="6">
         <v>3462</v>
@@ -12721,10 +12721,10 @@
     </row>
     <row r="125" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C125" s="6">
         <v>3108</v>
@@ -12803,10 +12803,10 @@
     </row>
     <row r="126" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C126" s="6">
         <v>2202</v>
@@ -12885,10 +12885,10 @@
     </row>
     <row r="127" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C127" s="6">
         <v>3666</v>
@@ -12967,10 +12967,10 @@
     </row>
     <row r="128" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C128" s="6">
         <v>3858</v>
@@ -13049,10 +13049,10 @@
     </row>
     <row r="129" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="C129" s="6">
         <v>2199</v>
@@ -13131,10 +13131,10 @@
     </row>
     <row r="130" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C130" s="6">
         <v>2709</v>
@@ -13213,10 +13213,10 @@
     </row>
     <row r="131" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C131" s="6">
         <v>2352</v>
@@ -13295,10 +13295,10 @@
     </row>
     <row r="132" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C132" s="6">
         <v>2373</v>
@@ -13377,10 +13377,10 @@
     </row>
     <row r="133" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C133" s="6">
         <v>2682</v>
@@ -13459,10 +13459,10 @@
     </row>
     <row r="134" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C134" s="6">
         <v>3066</v>
@@ -13541,10 +13541,10 @@
     </row>
     <row r="135" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C135" s="6">
         <v>2214</v>
@@ -13623,10 +13623,10 @@
     </row>
     <row r="136" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C136" s="6">
         <v>1926</v>
@@ -13705,10 +13705,10 @@
     </row>
     <row r="137" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A137" s="6" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>694</v>
+        <v>670</v>
       </c>
       <c r="C137" s="6">
         <v>2175</v>
@@ -13787,10 +13787,10 @@
     </row>
     <row r="138" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A138" s="6" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C138" s="6">
         <v>1962</v>
@@ -13869,10 +13869,10 @@
     </row>
     <row r="139" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A139" s="6" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C139" s="6">
         <v>2871</v>
@@ -13951,10 +13951,10 @@
     </row>
     <row r="140" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A140" s="6" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C140" s="6">
         <v>1983</v>
@@ -14033,10 +14033,10 @@
     </row>
     <row r="141" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A141" s="6" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C141" s="6">
         <v>1698</v>
@@ -14115,10 +14115,10 @@
     </row>
     <row r="142" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A142" s="6" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C142" s="6">
         <v>1941</v>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="143" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A143" s="6" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C143" s="6">
         <v>1620</v>
@@ -14279,10 +14279,10 @@
     </row>
     <row r="144" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A144" s="6" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="C144" s="6">
         <v>1302</v>
@@ -14361,10 +14361,10 @@
     </row>
     <row r="145" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A145" s="6" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="C145" s="6">
         <v>1851</v>
@@ -14443,10 +14443,10 @@
     </row>
     <row r="146" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A146" s="6" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="C146" s="6">
         <v>1917</v>
@@ -14525,10 +14525,10 @@
     </row>
     <row r="147" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A147" s="6" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="C147" s="6">
         <v>1581</v>
@@ -14607,10 +14607,10 @@
     </row>
     <row r="148" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A148" s="6" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="C148" s="6">
         <v>1482</v>
@@ -14689,10 +14689,10 @@
     </row>
     <row r="149" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A149" s="6" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="C149" s="6">
         <v>1848</v>
@@ -14771,10 +14771,10 @@
     </row>
     <row r="150" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A150" s="6" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="C150" s="6">
         <v>2226</v>
@@ -14853,10 +14853,10 @@
     </row>
     <row r="151" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A151" s="6" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C151" s="6">
         <v>1335</v>
@@ -14935,10 +14935,10 @@
     </row>
     <row r="152" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A152" s="6" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C152" s="6">
         <v>1842</v>
@@ -15017,10 +15017,10 @@
     </row>
     <row r="153" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C153" s="6">
         <v>2112</v>
@@ -15099,10 +15099,10 @@
     </row>
     <row r="154" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A154" s="6" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="C154" s="6">
         <v>1794</v>
@@ -15181,10 +15181,10 @@
     </row>
     <row r="155" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A155" s="6" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C155" s="6">
         <v>2112</v>
@@ -15263,10 +15263,10 @@
     </row>
     <row r="156" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A156" s="6" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="C156" s="6">
         <v>1314</v>
@@ -15345,10 +15345,10 @@
     </row>
     <row r="157" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A157" s="6" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="C157" s="6">
         <v>1224</v>
@@ -15427,10 +15427,10 @@
     </row>
     <row r="158" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A158" s="6" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C158" s="6">
         <v>1239</v>
@@ -15509,10 +15509,10 @@
     </row>
     <row r="159" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A159" s="6" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>695</v>
+        <v>671</v>
       </c>
       <c r="C159" s="6">
         <v>1188</v>
@@ -15591,10 +15591,10 @@
     </row>
     <row r="160" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A160" s="6" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C160" s="6">
         <v>1437</v>
@@ -15673,10 +15673,10 @@
     </row>
     <row r="161" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A161" s="6" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="C161" s="6">
         <v>1254</v>
@@ -15755,10 +15755,10 @@
     </row>
     <row r="162" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A162" s="6" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="C162" s="6">
         <v>1653</v>
@@ -15837,10 +15837,10 @@
     </row>
     <row r="163" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A163" s="6" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="C163" s="6">
         <v>1125</v>
@@ -15919,10 +15919,10 @@
     </row>
     <row r="164" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A164" s="6" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="C164" s="6">
         <v>1299</v>
@@ -16001,10 +16001,10 @@
     </row>
     <row r="165" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A165" s="6" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="C165" s="6">
         <v>1389</v>
@@ -16083,10 +16083,10 @@
     </row>
     <row r="166" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A166" s="6" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="C166" s="6">
         <v>1656</v>
@@ -16165,10 +16165,10 @@
     </row>
     <row r="167" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A167" s="6" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="C167" s="6">
         <v>2190</v>
@@ -16247,10 +16247,10 @@
     </row>
     <row r="168" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A168" s="6" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="C168" s="6">
         <v>1827</v>
@@ -16329,10 +16329,10 @@
     </row>
     <row r="169" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A169" s="6" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="C169" s="6">
         <v>1554</v>
@@ -16411,10 +16411,10 @@
     </row>
     <row r="170" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A170" s="6" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="C170" s="6">
         <v>2046</v>
@@ -16493,10 +16493,10 @@
     </row>
     <row r="171" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A171" s="6" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="C171" s="6">
         <v>1965</v>
@@ -16575,10 +16575,10 @@
     </row>
     <row r="172" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A172" s="6" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="C172" s="6">
         <v>2157</v>
@@ -16657,10 +16657,10 @@
     </row>
     <row r="173" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A173" s="6" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>696</v>
+        <v>672</v>
       </c>
       <c r="C173" s="6">
         <v>1701</v>
@@ -16739,10 +16739,10 @@
     </row>
     <row r="174" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A174" s="6" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C174" s="6">
         <v>1440</v>
@@ -16821,10 +16821,10 @@
     </row>
     <row r="175" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A175" s="6" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="C175" s="6">
         <v>1647</v>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="176" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A176" s="6" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C176" s="6">
         <v>1989</v>
@@ -16985,10 +16985,10 @@
     </row>
     <row r="177" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A177" s="6" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C177" s="6">
         <v>1971</v>
@@ -17067,10 +17067,10 @@
     </row>
     <row r="178" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A178" s="6" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C178" s="6">
         <v>2106</v>
@@ -17149,10 +17149,10 @@
     </row>
     <row r="179" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A179" s="6" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C179" s="6">
         <v>1359</v>
@@ -17231,10 +17231,10 @@
     </row>
     <row r="180" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A180" s="6" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="C180" s="6">
         <v>1332</v>
@@ -17313,10 +17313,10 @@
     </row>
     <row r="181" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="C181" s="6">
         <v>1380</v>
@@ -17395,10 +17395,10 @@
     </row>
     <row r="182" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A182" s="6" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="C182" s="6">
         <v>1356</v>
@@ -17477,10 +17477,10 @@
     </row>
     <row r="183" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A183" s="6" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="C183" s="6">
         <v>1740</v>
@@ -17559,10 +17559,10 @@
     </row>
     <row r="184" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A184" s="6" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="C184" s="6">
         <v>1473</v>
@@ -17641,10 +17641,10 @@
     </row>
     <row r="185" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A185" s="6" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="C185" s="6">
         <v>2952</v>
@@ -17723,10 +17723,10 @@
     </row>
     <row r="186" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A186" s="6" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C186" s="6">
         <v>2802</v>
@@ -17805,10 +17805,10 @@
     </row>
     <row r="187" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A187" s="6" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="C187" s="6">
         <v>2466</v>
@@ -17887,10 +17887,10 @@
     </row>
     <row r="188" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A188" s="6" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="C188" s="6">
         <v>2319</v>
@@ -17969,10 +17969,10 @@
     </row>
     <row r="189" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A189" s="6" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="C189" s="6">
         <v>3231</v>
@@ -18051,10 +18051,10 @@
     </row>
     <row r="190" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A190" s="6" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="C190" s="6">
         <v>3150</v>
@@ -18133,10 +18133,10 @@
     </row>
     <row r="191" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A191" s="6" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>697</v>
+        <v>673</v>
       </c>
       <c r="C191" s="6">
         <v>4035</v>
@@ -18215,10 +18215,10 @@
     </row>
     <row r="192" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A192" s="6" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="C192" s="6">
         <v>3072</v>
@@ -18297,10 +18297,10 @@
     </row>
     <row r="193" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A193" s="6" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="C193" s="6">
         <v>2595</v>
@@ -18379,10 +18379,10 @@
     </row>
     <row r="194" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A194" s="6" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="C194" s="6">
         <v>1290</v>
@@ -18461,10 +18461,10 @@
     </row>
     <row r="195" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A195" s="6" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="C195" s="6">
         <v>1971</v>
@@ -18543,10 +18543,10 @@
     </row>
     <row r="196" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A196" s="6" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C196" s="6">
         <v>1203</v>
@@ -18625,10 +18625,10 @@
     </row>
     <row r="197" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A197" s="6" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="C197" s="6">
         <v>1533</v>
@@ -18707,10 +18707,10 @@
     </row>
     <row r="198" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A198" s="6" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="C198" s="6">
         <v>2448</v>
@@ -18789,10 +18789,10 @@
     </row>
     <row r="199" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A199" s="6" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="C199" s="6">
         <v>1503</v>
@@ -18871,10 +18871,10 @@
     </row>
     <row r="200" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="C200" s="6">
         <v>1980</v>
@@ -18953,10 +18953,10 @@
     </row>
     <row r="201" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A201" s="6" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="C201" s="6">
         <v>2184</v>
@@ -19035,10 +19035,10 @@
     </row>
     <row r="202" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A202" s="6" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="C202" s="6">
         <v>2259</v>
@@ -19117,10 +19117,10 @@
     </row>
     <row r="203" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A203" s="6" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="C203" s="6">
         <v>1887</v>
@@ -19199,10 +19199,10 @@
     </row>
     <row r="204" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A204" s="6" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="C204" s="6">
         <v>2934</v>
@@ -19281,10 +19281,10 @@
     </row>
     <row r="205" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A205" s="6" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="C205" s="6">
         <v>3933</v>
@@ -19363,10 +19363,10 @@
     </row>
     <row r="206" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A206" s="6" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C206" s="6">
         <v>5070</v>
@@ -19445,10 +19445,10 @@
     </row>
     <row r="207" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A207" s="6" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="C207" s="6">
         <v>1830</v>
@@ -19527,10 +19527,10 @@
     </row>
     <row r="208" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A208" s="6" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C208" s="6">
         <v>1914</v>
@@ -19609,10 +19609,10 @@
     </row>
     <row r="209" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A209" s="6" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="C209" s="6">
         <v>1797</v>
@@ -19691,10 +19691,10 @@
     </row>
     <row r="210" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A210" s="6" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="C210" s="6">
         <v>1494</v>
@@ -19773,10 +19773,10 @@
     </row>
     <row r="211" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A211" s="6" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="C211" s="6">
         <v>3921</v>
@@ -19855,10 +19855,10 @@
     </row>
     <row r="212" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C212" s="6">
         <v>3435</v>
@@ -19937,10 +19937,10 @@
     </row>
     <row r="213" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A213" s="6" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="C213" s="6">
         <v>1446</v>
@@ -20019,10 +20019,10 @@
     </row>
     <row r="214" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A214" s="6" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C214" s="6">
         <v>1935</v>
@@ -20101,10 +20101,10 @@
     </row>
     <row r="215" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A215" s="6" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C215" s="6">
         <v>1689</v>
@@ -20183,10 +20183,10 @@
     </row>
     <row r="216" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A216" s="6" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="C216" s="6">
         <v>1710</v>
@@ -20265,10 +20265,10 @@
     </row>
     <row r="217" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A217" s="6" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="C217" s="6">
         <v>1434</v>
@@ -20347,10 +20347,10 @@
     </row>
     <row r="218" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A218" s="6" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="C218" s="6">
         <v>1716</v>
@@ -20429,10 +20429,10 @@
     </row>
     <row r="219" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A219" s="6" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="C219" s="6">
         <v>1089</v>
@@ -20511,10 +20511,10 @@
     </row>
     <row r="220" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A220" s="6" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C220" s="6">
         <v>1122</v>
@@ -20593,10 +20593,10 @@
     </row>
     <row r="221" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A221" s="6" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="C221" s="6">
         <v>1077</v>
@@ -20675,10 +20675,10 @@
     </row>
     <row r="222" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A222" s="6" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C222" s="6">
         <v>1170</v>
@@ -20757,10 +20757,10 @@
     </row>
     <row r="223" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A223" s="6" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C223" s="6">
         <v>1518</v>
@@ -20839,10 +20839,10 @@
     </row>
     <row r="224" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A224" s="6" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C224" s="6">
         <v>1419</v>
@@ -20921,10 +20921,10 @@
     </row>
     <row r="225" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A225" s="6" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C225" s="6">
         <v>1839</v>
@@ -21003,10 +21003,10 @@
     </row>
     <row r="226" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A226" s="6" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="C226" s="6">
         <v>1665</v>
@@ -21085,10 +21085,10 @@
     </row>
     <row r="227" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A227" s="6" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C227" s="6">
         <v>2169</v>
@@ -21167,10 +21167,10 @@
     </row>
     <row r="228" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A228" s="6" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C228" s="6">
         <v>1836</v>
@@ -21249,10 +21249,10 @@
     </row>
     <row r="229" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A229" s="6" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C229" s="6">
         <v>2088</v>
@@ -21331,10 +21331,10 @@
     </row>
     <row r="230" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A230" s="6" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C230" s="6">
         <v>1965</v>
@@ -21413,10 +21413,10 @@
     </row>
     <row r="231" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A231" s="6" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C231" s="6">
         <v>1842</v>
@@ -21495,10 +21495,10 @@
     </row>
     <row r="232" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A232" s="6" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="C232" s="6">
         <v>2331</v>
@@ -21577,10 +21577,10 @@
     </row>
     <row r="233" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A233" s="6" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="C233" s="6">
         <v>2700</v>
@@ -21659,10 +21659,10 @@
     </row>
     <row r="234" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A234" s="6" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="C234" s="6">
         <v>1986</v>
@@ -21741,10 +21741,10 @@
     </row>
     <row r="235" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A235" s="6" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="C235" s="6">
         <v>1545</v>
@@ -21823,10 +21823,10 @@
     </row>
     <row r="236" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A236" s="6" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="C236" s="6">
         <v>1383</v>
@@ -21905,10 +21905,10 @@
     </row>
     <row r="237" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A237" s="6" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="C237" s="6">
         <v>1644</v>
@@ -21987,10 +21987,10 @@
     </row>
     <row r="238" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A238" s="6" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="C238" s="6">
         <v>2163</v>
@@ -22069,10 +22069,10 @@
     </row>
     <row r="239" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A239" s="6" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C239" s="6">
         <v>2586</v>
@@ -22151,10 +22151,10 @@
     </row>
     <row r="240" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A240" s="6" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="C240" s="6">
         <v>2784</v>
@@ -22233,10 +22233,10 @@
     </row>
     <row r="241" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A241" s="6" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="C241" s="6">
         <v>2367</v>
@@ -22315,10 +22315,10 @@
     </row>
     <row r="242" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A242" s="6" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="C242" s="6">
         <v>2244</v>
@@ -22397,10 +22397,10 @@
     </row>
     <row r="243" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A243" s="6" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="C243" s="6">
         <v>1812</v>
@@ -22479,10 +22479,10 @@
     </row>
     <row r="244" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A244" s="6" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="C244" s="6">
         <v>1752</v>
@@ -22561,10 +22561,10 @@
     </row>
     <row r="245" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A245" s="6" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="C245" s="6">
         <v>2016</v>
@@ -22643,10 +22643,10 @@
     </row>
     <row r="246" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A246" s="6" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="C246" s="6">
         <v>1362</v>
@@ -22725,10 +22725,10 @@
     </row>
     <row r="247" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A247" s="6" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="C247" s="6">
         <v>1779</v>
@@ -22807,10 +22807,10 @@
     </row>
     <row r="248" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A248" s="6" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C248" s="6">
         <v>1410</v>
@@ -22889,10 +22889,10 @@
     </row>
     <row r="249" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A249" s="6" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="C249" s="6">
         <v>1851</v>
@@ -22971,10 +22971,10 @@
     </row>
     <row r="250" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A250" s="6" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C250" s="6">
         <v>1923</v>
@@ -23053,10 +23053,10 @@
     </row>
     <row r="251" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="C251" s="6">
         <v>2064</v>
@@ -23135,10 +23135,10 @@
     </row>
     <row r="252" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A252" s="6" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="C252" s="6">
         <v>2133</v>
@@ -23217,10 +23217,10 @@
     </row>
     <row r="253" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A253" s="6" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="C253" s="6">
         <v>1407</v>
@@ -23299,10 +23299,10 @@
     </row>
     <row r="254" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A254" s="6" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="C254" s="6">
         <v>1389</v>
@@ -23381,10 +23381,10 @@
     </row>
     <row r="255" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A255" s="6" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="C255" s="6">
         <v>2115</v>
@@ -23463,10 +23463,10 @@
     </row>
     <row r="256" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A256" s="6" t="s">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="C256" s="6">
         <v>1404</v>
@@ -23545,10 +23545,10 @@
     </row>
     <row r="257" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A257" s="6" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="C257" s="6">
         <v>1596</v>
@@ -23627,10 +23627,10 @@
     </row>
     <row r="258" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A258" s="6" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="C258" s="6">
         <v>1611</v>
@@ -23709,10 +23709,10 @@
     </row>
     <row r="259" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A259" s="6" t="s">
-        <v>534</v>
+        <v>510</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="C259" s="6">
         <v>2280</v>
@@ -23791,10 +23791,10 @@
     </row>
     <row r="260" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A260" s="6" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="C260" s="6">
         <v>1305</v>
@@ -23873,10 +23873,10 @@
     </row>
     <row r="261" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A261" s="6" t="s">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="C261" s="6">
         <v>1647</v>
@@ -23955,10 +23955,10 @@
     </row>
     <row r="262" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A262" s="6" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="C262" s="6">
         <v>1515</v>
@@ -24037,10 +24037,10 @@
     </row>
     <row r="263" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A263" s="6" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="C263" s="6">
         <v>1929</v>
@@ -24119,10 +24119,10 @@
     </row>
     <row r="264" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A264" s="6" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="C264" s="6">
         <v>1365</v>
@@ -24201,10 +24201,10 @@
     </row>
     <row r="265" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A265" s="6" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="C265" s="6">
         <v>1383</v>
@@ -24283,10 +24283,10 @@
     </row>
     <row r="266" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A266" s="6" t="s">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="C266" s="6">
         <v>1791</v>
@@ -24365,10 +24365,10 @@
     </row>
     <row r="267" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A267" s="6" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>698</v>
+        <v>674</v>
       </c>
       <c r="C267" s="6">
         <v>1563</v>
@@ -24447,10 +24447,10 @@
     </row>
     <row r="268" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A268" s="6" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="C268" s="6">
         <v>1341</v>
@@ -24529,10 +24529,10 @@
     </row>
     <row r="269" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A269" s="6" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="C269" s="6">
         <v>1947</v>
@@ -24611,10 +24611,10 @@
     </row>
     <row r="270" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A270" s="6" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
       <c r="C270" s="6">
         <v>1614</v>
@@ -24693,10 +24693,10 @@
     </row>
     <row r="271" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A271" s="6" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="C271" s="6">
         <v>1935</v>
@@ -24775,10 +24775,10 @@
     </row>
     <row r="272" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A272" s="6" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="C272" s="6">
         <v>1974</v>
@@ -24857,10 +24857,10 @@
     </row>
     <row r="273" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A273" s="6" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="C273" s="6">
         <v>1971</v>
@@ -24939,10 +24939,10 @@
     </row>
     <row r="274" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A274" s="6" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="C274" s="6">
         <v>2112</v>
@@ -25021,10 +25021,10 @@
     </row>
     <row r="275" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A275" s="6" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="C275" s="6">
         <v>2769</v>
@@ -25103,10 +25103,10 @@
     </row>
     <row r="276" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A276" s="6" t="s">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>567</v>
+        <v>543</v>
       </c>
       <c r="C276" s="6">
         <v>2019</v>
@@ -25185,10 +25185,10 @@
     </row>
     <row r="277" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A277" s="6" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C277" s="6">
         <v>2154</v>
@@ -25267,10 +25267,10 @@
     </row>
     <row r="278" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A278" s="6" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="C278" s="6">
         <v>2112</v>
@@ -25349,10 +25349,10 @@
     </row>
     <row r="279" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A279" s="6" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="C279" s="6">
         <v>2763</v>
@@ -25431,10 +25431,10 @@
     </row>
     <row r="280" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A280" s="6" t="s">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="C280" s="6">
         <v>1359</v>
@@ -25513,10 +25513,10 @@
     </row>
     <row r="281" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A281" s="6" t="s">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="C281" s="6">
         <v>1680</v>
@@ -25595,10 +25595,10 @@
     </row>
     <row r="282" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A282" s="6" t="s">
-        <v>577</v>
+        <v>553</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>701</v>
+        <v>677</v>
       </c>
       <c r="C282" s="6">
         <v>2310</v>
@@ -25677,10 +25677,10 @@
     </row>
     <row r="283" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A283" s="6" t="s">
-        <v>578</v>
+        <v>554</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C283" s="6">
         <v>2715</v>
@@ -25759,10 +25759,10 @@
     </row>
     <row r="284" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A284" s="6" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C284" s="6">
         <v>2253</v>
@@ -25841,10 +25841,10 @@
     </row>
     <row r="285" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A285" s="6" t="s">
-        <v>582</v>
+        <v>558</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C285" s="6">
         <v>2532</v>
@@ -25923,10 +25923,10 @@
     </row>
     <row r="286" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A286" s="6" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="C286" s="6">
         <v>2022</v>
@@ -26005,10 +26005,10 @@
     </row>
     <row r="287" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A287" s="6" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C287" s="6">
         <v>2904</v>
@@ -26087,10 +26087,10 @@
     </row>
     <row r="288" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A288" s="6" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="C288" s="6">
         <v>1923</v>
@@ -26169,10 +26169,10 @@
     </row>
     <row r="289" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A289" s="6" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="C289" s="6">
         <v>2328</v>
@@ -26251,10 +26251,10 @@
     </row>
     <row r="290" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A290" s="6" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="C290" s="6">
         <v>1977</v>
@@ -26333,10 +26333,10 @@
     </row>
     <row r="291" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A291" s="6" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="C291" s="6">
         <v>1611</v>
@@ -26415,10 +26415,10 @@
     </row>
     <row r="292" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A292" s="6" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="C292" s="6">
         <v>2151</v>
@@ -26497,10 +26497,10 @@
     </row>
     <row r="293" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A293" s="6" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C293" s="6">
         <v>2178</v>
@@ -26579,10 +26579,10 @@
     </row>
     <row r="294" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A294" s="6" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="C294" s="6">
         <v>1320</v>
@@ -26661,10 +26661,10 @@
     </row>
     <row r="295" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A295" s="6" t="s">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>603</v>
+        <v>579</v>
       </c>
       <c r="C295" s="6">
         <v>1206</v>
@@ -26743,10 +26743,10 @@
     </row>
     <row r="296" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A296" s="6" t="s">
-        <v>604</v>
+        <v>580</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="C296" s="6">
         <v>1389</v>
@@ -26825,10 +26825,10 @@
     </row>
     <row r="297" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A297" s="6" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="C297" s="6">
         <v>1356</v>
@@ -26907,10 +26907,10 @@
     </row>
     <row r="298" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A298" s="6" t="s">
-        <v>608</v>
+        <v>584</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="C298" s="6">
         <v>1212</v>
@@ -26989,10 +26989,10 @@
     </row>
     <row r="299" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A299" s="6" t="s">
-        <v>610</v>
+        <v>586</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>611</v>
+        <v>587</v>
       </c>
       <c r="C299" s="6">
         <v>1902</v>
@@ -27071,10 +27071,10 @@
     </row>
     <row r="300" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A300" s="6" t="s">
-        <v>612</v>
+        <v>588</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="C300" s="6">
         <v>1359</v>
@@ -27153,10 +27153,10 @@
     </row>
     <row r="301" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A301" s="6" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C301" s="6">
         <v>1212</v>
@@ -27235,10 +27235,10 @@
     </row>
     <row r="302" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A302" s="6" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C302" s="6">
         <v>1227</v>
@@ -27316,10 +27316,10 @@
     </row>
     <row r="303" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A303" s="6" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="C303" s="6">
         <v>1242</v>
@@ -27397,10 +27397,10 @@
     </row>
     <row r="304" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A304" s="6" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="C304" s="6">
         <v>1254</v>
@@ -27478,10 +27478,10 @@
     </row>
     <row r="305" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A305" s="6" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
       <c r="C305" s="6">
         <v>1266</v>
@@ -27559,10 +27559,10 @@
     </row>
     <row r="306" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A306" s="6" t="s">
-        <v>620</v>
+        <v>596</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>621</v>
+        <v>597</v>
       </c>
       <c r="C306" s="6">
         <v>1275</v>
@@ -27640,10 +27640,10 @@
     </row>
     <row r="307" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A307" s="6" t="s">
-        <v>622</v>
+        <v>598</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>623</v>
+        <v>599</v>
       </c>
       <c r="C307" s="6">
         <v>1287</v>
@@ -27721,10 +27721,10 @@
     </row>
     <row r="308" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A308" s="6" t="s">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>625</v>
+        <v>601</v>
       </c>
       <c r="C308" s="6">
         <v>1293</v>
@@ -27802,10 +27802,10 @@
     </row>
     <row r="309" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A309" s="6" t="s">
-        <v>626</v>
+        <v>602</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>627</v>
+        <v>603</v>
       </c>
       <c r="C309" s="6">
         <v>1299</v>
@@ -27883,10 +27883,10 @@
     </row>
     <row r="310" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A310" s="6" t="s">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="C310" s="6">
         <v>1305</v>
@@ -27964,10 +27964,10 @@
     </row>
     <row r="311" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A311" s="6" t="s">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>631</v>
+        <v>607</v>
       </c>
       <c r="C311" s="6">
         <v>1308</v>
@@ -28045,10 +28045,10 @@
     </row>
     <row r="312" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A312" s="6" t="s">
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="C312" s="6">
         <v>1314</v>
@@ -28126,10 +28126,10 @@
     </row>
     <row r="313" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A313" s="6" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>635</v>
+        <v>611</v>
       </c>
       <c r="C313" s="6">
         <v>1320</v>
@@ -28207,10 +28207,10 @@
     </row>
     <row r="314" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A314" s="6" t="s">
-        <v>636</v>
+        <v>612</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>637</v>
+        <v>613</v>
       </c>
       <c r="C314" s="6">
         <v>1326</v>
@@ -28288,10 +28288,10 @@
     </row>
     <row r="315" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A315" s="6" t="s">
-        <v>638</v>
+        <v>614</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>639</v>
+        <v>615</v>
       </c>
       <c r="C315" s="6">
         <v>1335</v>
@@ -28369,10 +28369,10 @@
     </row>
     <row r="316" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A316" s="6" t="s">
-        <v>640</v>
+        <v>616</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="C316" s="6">
         <v>1341</v>
@@ -28450,10 +28450,10 @@
     </row>
     <row r="317" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A317" s="6" t="s">
-        <v>642</v>
+        <v>618</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="C317" s="6">
         <v>1356</v>
@@ -28531,10 +28531,10 @@
     </row>
     <row r="318" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A318" s="6" t="s">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>645</v>
+        <v>621</v>
       </c>
       <c r="C318" s="6">
         <v>1368</v>
@@ -28612,10 +28612,10 @@
     </row>
     <row r="319" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A319" s="6" t="s">
-        <v>646</v>
+        <v>622</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>647</v>
+        <v>623</v>
       </c>
       <c r="C319" s="6">
         <v>1389</v>
@@ -28693,10 +28693,10 @@
     </row>
     <row r="320" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A320" s="6" t="s">
-        <v>648</v>
+        <v>624</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="C320" s="6">
         <v>1413</v>
@@ -28774,10 +28774,10 @@
     </row>
     <row r="321" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A321" s="6" t="s">
-        <v>650</v>
+        <v>626</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C321" s="6">
         <v>1434</v>
@@ -28855,10 +28855,10 @@
     </row>
     <row r="322" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A322" s="6" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="C322" s="6">
         <v>1461</v>
@@ -28936,10 +28936,10 @@
     </row>
     <row r="323" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A323" s="6" t="s">
-        <v>654</v>
+        <v>630</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>655</v>
+        <v>631</v>
       </c>
       <c r="C323" s="6">
         <v>1491</v>
@@ -29017,10 +29017,10 @@
     </row>
     <row r="324" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A324" s="6" t="s">
-        <v>656</v>
+        <v>632</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>657</v>
+        <v>633</v>
       </c>
       <c r="C324" s="6">
         <v>1533</v>
@@ -29098,10 +29098,10 @@
     </row>
     <row r="325" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A325" s="6" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="C325" s="6">
         <v>1578</v>
@@ -29179,10 +29179,10 @@
     </row>
     <row r="326" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A326" s="6" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="C326" s="6">
         <v>1620</v>
@@ -29260,10 +29260,10 @@
     </row>
     <row r="327" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A327" s="6" t="s">
-        <v>662</v>
+        <v>638</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="C327" s="6">
         <v>1656</v>
@@ -29341,10 +29341,10 @@
     </row>
     <row r="328" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A328" s="6" t="s">
-        <v>664</v>
+        <v>640</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>665</v>
+        <v>641</v>
       </c>
       <c r="C328" s="6">
         <v>1689</v>
@@ -29422,10 +29422,10 @@
     </row>
     <row r="329" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A329" s="6" t="s">
-        <v>666</v>
+        <v>642</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="C329" s="6">
         <v>1719</v>
@@ -29503,10 +29503,10 @@
     </row>
     <row r="330" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A330" s="6" t="s">
-        <v>668</v>
+        <v>644</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="C330" s="6">
         <v>1752</v>
@@ -29584,10 +29584,10 @@
     </row>
     <row r="331" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A331" s="6" t="s">
-        <v>670</v>
+        <v>646</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>671</v>
+        <v>647</v>
       </c>
       <c r="C331" s="6">
         <v>1785</v>
@@ -29665,10 +29665,10 @@
     </row>
     <row r="332" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A332" s="6" t="s">
-        <v>672</v>
+        <v>648</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="C332" s="6">
         <v>1833</v>
@@ -29746,10 +29746,10 @@
     </row>
     <row r="333" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A333" s="6" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="C333" s="6">
         <v>1905</v>
@@ -29827,10 +29827,10 @@
     </row>
     <row r="334" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A334" s="6" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="B334" s="5" t="s">
-        <v>677</v>
+        <v>653</v>
       </c>
       <c r="C334" s="6">
         <v>1980</v>
@@ -29908,10 +29908,10 @@
     </row>
     <row r="335" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A335" s="6" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="B335" s="5" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="C335" s="6">
         <v>2076</v>
@@ -29989,10 +29989,10 @@
     </row>
     <row r="336" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A336" s="6" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="B336" s="5" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="C336" s="6">
         <v>2232</v>
@@ -30070,10 +30070,10 @@
     </row>
     <row r="337" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A337" s="6" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="C337" s="6">
         <v>2325</v>
@@ -30151,10 +30151,10 @@
     </row>
     <row r="338" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A338" s="6" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="B338" s="5" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="C338" s="6">
         <v>2460</v>
@@ -30232,10 +30232,10 @@
     </row>
     <row r="339" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A339" s="6" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="C339" s="5">
         <v>2793</v>
@@ -31715,89 +31715,89 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>1</v>
+        <v>678</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>2</v>
+        <v>679</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>3</v>
+        <v>680</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>4</v>
+        <v>682</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>5</v>
+        <v>681</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>6</v>
+        <v>683</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>7</v>
+        <v>684</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>8</v>
+        <v>685</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>9</v>
+        <v>686</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>10</v>
+        <v>687</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>11</v>
+        <v>688</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>12</v>
+        <v>689</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>13</v>
+        <v>690</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>14</v>
+        <v>691</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>15</v>
+        <v>692</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>16</v>
+        <v>693</v>
       </c>
       <c r="S1" s="7" t="s">
-        <v>17</v>
+        <v>694</v>
       </c>
       <c r="T1" s="7" t="s">
-        <v>18</v>
+        <v>695</v>
       </c>
       <c r="U1" s="7" t="s">
-        <v>19</v>
+        <v>696</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>20</v>
+        <v>697</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>21</v>
+        <v>698</v>
       </c>
       <c r="X1" s="7" t="s">
-        <v>22</v>
+        <v>699</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>23</v>
+        <v>700</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>24</v>
+        <v>701</v>
       </c>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
     <row r="2" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C2" s="9">
         <v>1749</v>
@@ -31876,10 +31876,10 @@
     </row>
     <row r="3" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C3" s="9">
         <v>1569</v>
@@ -31958,10 +31958,10 @@
     </row>
     <row r="4" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C4" s="9">
         <v>1740</v>
@@ -32040,10 +32040,10 @@
     </row>
     <row r="5" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C5" s="9">
         <v>1701</v>
@@ -32122,10 +32122,10 @@
     </row>
     <row r="6" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C6" s="9">
         <v>1671</v>
@@ -32204,10 +32204,10 @@
     </row>
     <row r="7" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="C7" s="9">
         <v>1497</v>
@@ -32286,10 +32286,10 @@
     </row>
     <row r="8" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C8" s="9">
         <v>918</v>
@@ -32368,10 +32368,10 @@
     </row>
     <row r="9" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>688</v>
+        <v>664</v>
       </c>
       <c r="C9" s="9">
         <v>1137</v>
@@ -32450,10 +32450,10 @@
     </row>
     <row r="10" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="C10" s="9">
         <v>1317</v>
@@ -32532,10 +32532,10 @@
     </row>
     <row r="11" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C11" s="9">
         <v>1281</v>
@@ -32614,10 +32614,10 @@
     </row>
     <row r="12" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="C12" s="9">
         <v>1236</v>
@@ -32696,10 +32696,10 @@
     </row>
     <row r="13" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C13" s="9">
         <v>1314</v>
@@ -32778,10 +32778,10 @@
     </row>
     <row r="14" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C14" s="9">
         <v>1443</v>
@@ -32860,10 +32860,10 @@
     </row>
     <row r="15" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C15" s="9">
         <v>1320</v>
@@ -32942,10 +32942,10 @@
     </row>
     <row r="16" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C16" s="9">
         <v>873</v>
@@ -33024,10 +33024,10 @@
     </row>
     <row r="17" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C17" s="9">
         <v>1173</v>
@@ -33106,10 +33106,10 @@
     </row>
     <row r="18" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C18" s="9">
         <v>1644</v>
@@ -33188,10 +33188,10 @@
     </row>
     <row r="19" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C19" s="9">
         <v>1260</v>
@@ -33270,10 +33270,10 @@
     </row>
     <row r="20" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="C20" s="9">
         <v>1266</v>
@@ -33352,10 +33352,10 @@
     </row>
     <row r="21" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C21" s="9">
         <v>1176</v>
@@ -33434,10 +33434,10 @@
     </row>
     <row r="22" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="C22" s="9">
         <v>2562</v>
@@ -33516,10 +33516,10 @@
     </row>
     <row r="23" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C23" s="9">
         <v>3447</v>
@@ -33598,10 +33598,10 @@
     </row>
     <row r="24" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="C24" s="9">
         <v>1161</v>
@@ -33680,10 +33680,10 @@
     </row>
     <row r="25" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C25" s="9">
         <v>1605</v>
@@ -33762,10 +33762,10 @@
     </row>
     <row r="26" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C26" s="9">
         <v>1590</v>
@@ -33844,10 +33844,10 @@
     </row>
     <row r="27" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="C27" s="9">
         <v>2757</v>
@@ -33926,10 +33926,10 @@
     </row>
     <row r="28" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="C28" s="9">
         <v>2700</v>
@@ -34008,10 +34008,10 @@
     </row>
     <row r="29" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C29" s="9">
         <v>2352</v>
@@ -34090,10 +34090,10 @@
     </row>
     <row r="30" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="C30" s="9">
         <v>2442</v>
@@ -34172,10 +34172,10 @@
     </row>
     <row r="31" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="C31" s="9">
         <v>1458</v>
@@ -34254,10 +34254,10 @@
     </row>
     <row r="32" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C32" s="9">
         <v>2193</v>
@@ -34336,10 +34336,10 @@
     </row>
     <row r="33" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C33" s="9">
         <v>1683</v>
@@ -34418,10 +34418,10 @@
     </row>
     <row r="34" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C34" s="9">
         <v>2217</v>
@@ -34500,10 +34500,10 @@
     </row>
     <row r="35" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C35" s="9">
         <v>1980</v>
@@ -34582,10 +34582,10 @@
     </row>
     <row r="36" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C36" s="9">
         <v>1836</v>
@@ -34664,10 +34664,10 @@
     </row>
     <row r="37" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="C37" s="9">
         <v>2448</v>
@@ -34746,10 +34746,10 @@
     </row>
     <row r="38" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C38" s="9">
         <v>2595</v>
@@ -34828,10 +34828,10 @@
     </row>
     <row r="39" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="C39" s="9">
         <v>2748</v>
@@ -34910,10 +34910,10 @@
     </row>
     <row r="40" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C40" s="9">
         <v>2337</v>
@@ -34992,10 +34992,10 @@
     </row>
     <row r="41" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="C41" s="9">
         <v>2343</v>
@@ -35074,10 +35074,10 @@
     </row>
     <row r="42" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C42" s="9">
         <v>1398</v>
@@ -35156,10 +35156,10 @@
     </row>
     <row r="43" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="C43" s="9">
         <v>3174</v>
@@ -35238,10 +35238,10 @@
     </row>
     <row r="44" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="C44" s="9">
         <v>2154</v>
@@ -35320,10 +35320,10 @@
     </row>
     <row r="45" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C45" s="9">
         <v>1506</v>
@@ -35402,10 +35402,10 @@
     </row>
     <row r="46" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="C46" s="9">
         <v>1530</v>
@@ -35484,10 +35484,10 @@
     </row>
     <row r="47" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C47" s="9">
         <v>1848</v>
@@ -35566,10 +35566,10 @@
     </row>
     <row r="48" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C48" s="9">
         <v>1935</v>
@@ -35648,10 +35648,10 @@
     </row>
     <row r="49" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C49" s="9">
         <v>1692</v>
@@ -35730,10 +35730,10 @@
     </row>
     <row r="50" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C50" s="9">
         <v>1611</v>
@@ -35812,10 +35812,10 @@
     </row>
     <row r="51" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C51" s="9">
         <v>1905</v>
@@ -35894,10 +35894,10 @@
     </row>
     <row r="52" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C52" s="9">
         <v>1863</v>
@@ -35976,10 +35976,10 @@
     </row>
     <row r="53" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C53" s="9">
         <v>1881</v>
@@ -36058,10 +36058,10 @@
     </row>
     <row r="54" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="C54" s="9">
         <v>2352</v>
@@ -36140,10 +36140,10 @@
     </row>
     <row r="55" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="C55" s="9">
         <v>2283</v>
@@ -36222,10 +36222,10 @@
     </row>
     <row r="56" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C56" s="9">
         <v>1761</v>
@@ -36304,10 +36304,10 @@
     </row>
     <row r="57" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C57" s="9">
         <v>2004</v>
@@ -36386,10 +36386,10 @@
     </row>
     <row r="58" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="C58" s="9">
         <v>1560</v>
@@ -36468,10 +36468,10 @@
     </row>
     <row r="59" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C59" s="9">
         <v>1671</v>
@@ -36550,10 +36550,10 @@
     </row>
     <row r="60" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C60" s="9">
         <v>1821</v>
@@ -36632,10 +36632,10 @@
     </row>
     <row r="61" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C61" s="9">
         <v>2532</v>
@@ -36714,10 +36714,10 @@
     </row>
     <row r="62" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C62" s="9">
         <v>1797</v>
@@ -36796,10 +36796,10 @@
     </row>
     <row r="63" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C63" s="9">
         <v>1719</v>
@@ -36878,10 +36878,10 @@
     </row>
     <row r="64" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C64" s="9">
         <v>1497</v>
@@ -36960,10 +36960,10 @@
     </row>
     <row r="65" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="C65" s="9">
         <v>1332</v>
@@ -37042,10 +37042,10 @@
     </row>
     <row r="66" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C66" s="9">
         <v>1944</v>
@@ -37124,10 +37124,10 @@
     </row>
     <row r="67" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C67" s="9">
         <v>2367</v>
@@ -37206,10 +37206,10 @@
     </row>
     <row r="68" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C68" s="9">
         <v>1728</v>
@@ -37288,10 +37288,10 @@
     </row>
     <row r="69" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C69" s="9">
         <v>2997</v>
@@ -37370,10 +37370,10 @@
     </row>
     <row r="70" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C70" s="9">
         <v>1650</v>
@@ -37452,10 +37452,10 @@
     </row>
     <row r="71" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="C71" s="9">
         <v>1950</v>
@@ -37534,10 +37534,10 @@
     </row>
     <row r="72" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C72" s="9">
         <v>2121</v>
@@ -37616,10 +37616,10 @@
     </row>
     <row r="73" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C73" s="9">
         <v>1752</v>
@@ -37698,10 +37698,10 @@
     </row>
     <row r="74" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C74" s="9">
         <v>1041</v>
@@ -37780,10 +37780,10 @@
     </row>
     <row r="75" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="C75" s="9">
         <v>1431</v>
@@ -37862,10 +37862,10 @@
     </row>
     <row r="76" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C76" s="9">
         <v>1644</v>
@@ -37944,10 +37944,10 @@
     </row>
     <row r="77" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="C77" s="9">
         <v>1308</v>
@@ -38026,10 +38026,10 @@
     </row>
     <row r="78" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C78" s="9">
         <v>1335</v>
@@ -38108,10 +38108,10 @@
     </row>
     <row r="79" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="C79" s="9">
         <v>1788</v>
@@ -38190,10 +38190,10 @@
     </row>
     <row r="80" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="C80" s="9">
         <v>1704</v>
@@ -38272,10 +38272,10 @@
     </row>
     <row r="81" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C81" s="9">
         <v>1680</v>
@@ -38354,10 +38354,10 @@
     </row>
     <row r="82" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="C82" s="9">
         <v>1245</v>
@@ -38436,10 +38436,10 @@
     </row>
     <row r="83" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="C83" s="9">
         <v>2838</v>
@@ -38518,10 +38518,10 @@
     </row>
     <row r="84" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C84" s="9">
         <v>2403</v>
@@ -38600,10 +38600,10 @@
     </row>
     <row r="85" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C85" s="9">
         <v>2454</v>
@@ -38682,10 +38682,10 @@
     </row>
     <row r="86" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="C86" s="9">
         <v>2589</v>
@@ -38764,10 +38764,10 @@
     </row>
     <row r="87" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C87" s="9">
         <v>1107</v>
@@ -38846,10 +38846,10 @@
     </row>
     <row r="88" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="C88" s="9">
         <v>1668</v>
@@ -38928,10 +38928,10 @@
     </row>
     <row r="89" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="C89" s="9">
         <v>1512</v>
@@ -39010,10 +39010,10 @@
     </row>
     <row r="90" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C90" s="9">
         <v>1071</v>
@@ -39092,10 +39092,10 @@
     </row>
     <row r="91" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C91" s="9">
         <v>1329</v>
@@ -39174,10 +39174,10 @@
     </row>
     <row r="92" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A92" s="8" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C92" s="9">
         <v>1029</v>
@@ -39256,10 +39256,10 @@
     </row>
     <row r="93" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A93" s="8" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C93" s="9">
         <v>1563</v>
@@ -39338,10 +39338,10 @@
     </row>
     <row r="94" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C94" s="9">
         <v>1173</v>
@@ -39420,10 +39420,10 @@
     </row>
     <row r="95" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C95" s="9">
         <v>2268</v>
@@ -39502,10 +39502,10 @@
     </row>
     <row r="96" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="C96" s="9">
         <v>1026</v>
@@ -39584,10 +39584,10 @@
     </row>
     <row r="97" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C97" s="9">
         <v>1356</v>
@@ -39666,10 +39666,10 @@
     </row>
     <row r="98" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C98" s="9">
         <v>1251</v>
@@ -39748,10 +39748,10 @@
     </row>
     <row r="99" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C99" s="9">
         <v>1041</v>
@@ -39830,10 +39830,10 @@
     </row>
     <row r="100" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="C100" s="9">
         <v>1236</v>
@@ -39912,10 +39912,10 @@
     </row>
     <row r="101" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="C101" s="9">
         <v>987</v>
@@ -39994,10 +39994,10 @@
     </row>
     <row r="102" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C102" s="9">
         <v>1026</v>
@@ -40076,10 +40076,10 @@
     </row>
     <row r="103" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A103" s="8" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C103" s="9">
         <v>1347</v>
@@ -40158,10 +40158,10 @@
     </row>
     <row r="104" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C104" s="9">
         <v>1020</v>
@@ -40240,10 +40240,10 @@
     </row>
     <row r="105" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A105" s="8" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C105" s="9">
         <v>1467</v>
@@ -40322,10 +40322,10 @@
     </row>
     <row r="106" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A106" s="8" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C106" s="9">
         <v>1212</v>
@@ -40404,10 +40404,10 @@
     </row>
     <row r="107" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A107" s="8" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="C107" s="9">
         <v>1341</v>
@@ -40486,10 +40486,10 @@
     </row>
     <row r="108" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A108" s="8" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="C108" s="9">
         <v>1179</v>
@@ -40568,10 +40568,10 @@
     </row>
     <row r="109" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A109" s="8" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="C109" s="9">
         <v>918</v>
@@ -40650,10 +40650,10 @@
     </row>
     <row r="110" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A110" s="8" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C110" s="9">
         <v>993</v>
@@ -40732,10 +40732,10 @@
     </row>
     <row r="111" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A111" s="8" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
       <c r="C111" s="9">
         <v>939</v>
@@ -40814,10 +40814,10 @@
     </row>
     <row r="112" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A112" s="8" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C112" s="9">
         <v>1368</v>
@@ -40896,10 +40896,10 @@
     </row>
     <row r="113" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A113" s="8" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>693</v>
+        <v>669</v>
       </c>
       <c r="C113" s="9">
         <v>885</v>
@@ -40978,10 +40978,10 @@
     </row>
     <row r="114" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A114" s="8" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C114" s="9">
         <v>1293</v>
@@ -41060,10 +41060,10 @@
     </row>
     <row r="115" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="C115" s="9">
         <v>1161</v>
@@ -41142,10 +41142,10 @@
     </row>
     <row r="116" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C116" s="9">
         <v>1155</v>
@@ -41224,10 +41224,10 @@
     </row>
     <row r="117" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>255</v>
+        <v>231</v>
       </c>
       <c r="C117" s="9">
         <v>1131</v>
@@ -41306,10 +41306,10 @@
     </row>
     <row r="118" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
-        <v>256</v>
+        <v>232</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>257</v>
+        <v>233</v>
       </c>
       <c r="C118" s="9">
         <v>1026</v>
@@ -41388,10 +41388,10 @@
     </row>
     <row r="119" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
-        <v>258</v>
+        <v>234</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="C119" s="9">
         <v>906</v>
@@ -41470,10 +41470,10 @@
     </row>
     <row r="120" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A120" s="8" t="s">
-        <v>260</v>
+        <v>236</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>261</v>
+        <v>237</v>
       </c>
       <c r="C120" s="9">
         <v>2925</v>
@@ -41552,10 +41552,10 @@
     </row>
     <row r="121" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C121" s="9">
         <v>3147</v>
@@ -41634,10 +41634,10 @@
     </row>
     <row r="122" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C122" s="9">
         <v>2334</v>
@@ -41716,10 +41716,10 @@
     </row>
     <row r="123" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="C123" s="9">
         <v>2376</v>
@@ -41798,10 +41798,10 @@
     </row>
     <row r="124" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="C124" s="9">
         <v>2829</v>
@@ -41880,10 +41880,10 @@
     </row>
     <row r="125" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="C125" s="9">
         <v>2454</v>
@@ -41962,10 +41962,10 @@
     </row>
     <row r="126" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="C126" s="9">
         <v>1692</v>
@@ -42044,10 +42044,10 @@
     </row>
     <row r="127" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="C127" s="9">
         <v>2751</v>
@@ -42126,10 +42126,10 @@
     </row>
     <row r="128" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
-        <v>276</v>
+        <v>252</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="C128" s="9">
         <v>2970</v>
@@ -42208,10 +42208,10 @@
     </row>
     <row r="129" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="C129" s="9">
         <v>1848</v>
@@ -42290,10 +42290,10 @@
     </row>
     <row r="130" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>281</v>
+        <v>257</v>
       </c>
       <c r="C130" s="9">
         <v>2256</v>
@@ -42372,10 +42372,10 @@
     </row>
     <row r="131" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
-        <v>282</v>
+        <v>258</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="C131" s="9">
         <v>1824</v>
@@ -42454,10 +42454,10 @@
     </row>
     <row r="132" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
-        <v>284</v>
+        <v>260</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>285</v>
+        <v>261</v>
       </c>
       <c r="C132" s="9">
         <v>2010</v>
@@ -42536,10 +42536,10 @@
     </row>
     <row r="133" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C133" s="9">
         <v>2166</v>
@@ -42618,10 +42618,10 @@
     </row>
     <row r="134" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="C134" s="9">
         <v>2376</v>
@@ -42700,10 +42700,10 @@
     </row>
     <row r="135" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="C135" s="9">
         <v>1845</v>
@@ -42782,10 +42782,10 @@
     </row>
     <row r="136" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C136" s="9">
         <v>1554</v>
@@ -42864,10 +42864,10 @@
     </row>
     <row r="137" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>694</v>
+        <v>670</v>
       </c>
       <c r="C137" s="9">
         <v>1632</v>
@@ -42946,10 +42946,10 @@
     </row>
     <row r="138" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="C138" s="9">
         <v>1473</v>
@@ -43028,10 +43028,10 @@
     </row>
     <row r="139" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="C139" s="9">
         <v>2181</v>
@@ -43110,10 +43110,10 @@
     </row>
     <row r="140" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="C140" s="9">
         <v>1488</v>
@@ -43192,10 +43192,10 @@
     </row>
     <row r="141" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="C141" s="9">
         <v>1275</v>
@@ -43274,10 +43274,10 @@
     </row>
     <row r="142" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="C142" s="9">
         <v>1455</v>
@@ -43356,10 +43356,10 @@
     </row>
     <row r="143" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="C143" s="9">
         <v>1215</v>
@@ -43438,10 +43438,10 @@
     </row>
     <row r="144" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="C144" s="9">
         <v>978</v>
@@ -43520,10 +43520,10 @@
     </row>
     <row r="145" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="C145" s="9">
         <v>1554</v>
@@ -43602,10 +43602,10 @@
     </row>
     <row r="146" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="C146" s="9">
         <v>1554</v>
@@ -43684,10 +43684,10 @@
     </row>
     <row r="147" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>313</v>
+        <v>289</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>314</v>
+        <v>290</v>
       </c>
       <c r="C147" s="9">
         <v>1185</v>
@@ -43766,10 +43766,10 @@
     </row>
     <row r="148" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>315</v>
+        <v>291</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="C148" s="9">
         <v>1113</v>
@@ -43848,10 +43848,10 @@
     </row>
     <row r="149" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>317</v>
+        <v>293</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="C149" s="9">
         <v>1386</v>
@@ -43930,10 +43930,10 @@
     </row>
     <row r="150" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="C150" s="9">
         <v>1674</v>
@@ -44012,10 +44012,10 @@
     </row>
     <row r="151" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C151" s="9">
         <v>1002</v>
@@ -44094,10 +44094,10 @@
     </row>
     <row r="152" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A152" s="8" t="s">
-        <v>323</v>
+        <v>299</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C152" s="9">
         <v>1404</v>
@@ -44176,10 +44176,10 @@
     </row>
     <row r="153" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A153" s="8" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="C153" s="9">
         <v>1584</v>
@@ -44258,10 +44258,10 @@
     </row>
     <row r="154" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A154" s="8" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="C154" s="9">
         <v>1347</v>
@@ -44340,10 +44340,10 @@
     </row>
     <row r="155" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A155" s="8" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>330</v>
+        <v>306</v>
       </c>
       <c r="C155" s="9">
         <v>1584</v>
@@ -44422,10 +44422,10 @@
     </row>
     <row r="156" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A156" s="8" t="s">
-        <v>331</v>
+        <v>307</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="C156" s="9">
         <v>996</v>
@@ -44504,10 +44504,10 @@
     </row>
     <row r="157" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A157" s="8" t="s">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>334</v>
+        <v>310</v>
       </c>
       <c r="C157" s="9">
         <v>1119</v>
@@ -44586,10 +44586,10 @@
     </row>
     <row r="158" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A158" s="8" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="C158" s="9">
         <v>984</v>
@@ -44668,10 +44668,10 @@
     </row>
     <row r="159" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A159" s="8" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>695</v>
+        <v>671</v>
       </c>
       <c r="C159" s="9">
         <v>981</v>
@@ -44750,10 +44750,10 @@
     </row>
     <row r="160" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A160" s="8" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="C160" s="9">
         <v>1254</v>
@@ -44832,10 +44832,10 @@
     </row>
     <row r="161" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A161" s="8" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="C161" s="9">
         <v>1053</v>
@@ -44914,10 +44914,10 @@
     </row>
     <row r="162" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
-        <v>342</v>
+        <v>318</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="C162" s="9">
         <v>1275</v>
@@ -44996,10 +44996,10 @@
     </row>
     <row r="163" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="C163" s="9">
         <v>888</v>
@@ -45078,10 +45078,10 @@
     </row>
     <row r="164" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
-        <v>346</v>
+        <v>322</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>347</v>
+        <v>323</v>
       </c>
       <c r="C164" s="9">
         <v>1089</v>
@@ -45160,10 +45160,10 @@
     </row>
     <row r="165" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
-        <v>348</v>
+        <v>324</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>349</v>
+        <v>325</v>
       </c>
       <c r="C165" s="9">
         <v>1095</v>
@@ -45242,10 +45242,10 @@
     </row>
     <row r="166" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="C166" s="9">
         <v>1383</v>
@@ -45324,10 +45324,10 @@
     </row>
     <row r="167" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A167" s="8" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>353</v>
+        <v>329</v>
       </c>
       <c r="C167" s="9">
         <v>1668</v>
@@ -45406,10 +45406,10 @@
     </row>
     <row r="168" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="C168" s="9">
         <v>1665</v>
@@ -45488,10 +45488,10 @@
     </row>
     <row r="169" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
-        <v>356</v>
+        <v>332</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="C169" s="9">
         <v>1266</v>
@@ -45570,10 +45570,10 @@
     </row>
     <row r="170" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
-        <v>358</v>
+        <v>334</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="C170" s="9">
         <v>1566</v>
@@ -45652,10 +45652,10 @@
     </row>
     <row r="171" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>361</v>
+        <v>337</v>
       </c>
       <c r="C171" s="9">
         <v>1584</v>
@@ -45734,10 +45734,10 @@
     </row>
     <row r="172" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
-        <v>362</v>
+        <v>338</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="C172" s="9">
         <v>1692</v>
@@ -45816,10 +45816,10 @@
     </row>
     <row r="173" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
-        <v>364</v>
+        <v>340</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>696</v>
+        <v>672</v>
       </c>
       <c r="C173" s="9">
         <v>1377</v>
@@ -45898,10 +45898,10 @@
     </row>
     <row r="174" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="C174" s="9">
         <v>1245</v>
@@ -45980,10 +45980,10 @@
     </row>
     <row r="175" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>368</v>
+        <v>344</v>
       </c>
       <c r="C175" s="9">
         <v>1236</v>
@@ -46062,10 +46062,10 @@
     </row>
     <row r="176" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
       <c r="C176" s="9">
         <v>1548</v>
@@ -46144,10 +46144,10 @@
     </row>
     <row r="177" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C177" s="9">
         <v>1542</v>
@@ -46226,10 +46226,10 @@
     </row>
     <row r="178" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
       <c r="C178" s="9">
         <v>1629</v>
@@ -46308,10 +46308,10 @@
     </row>
     <row r="179" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C179" s="9">
         <v>1038</v>
@@ -46390,10 +46390,10 @@
     </row>
     <row r="180" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="C180" s="9">
         <v>1041</v>
@@ -46472,10 +46472,10 @@
     </row>
     <row r="181" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="C181" s="9">
         <v>1071</v>
@@ -46554,10 +46554,10 @@
     </row>
     <row r="182" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>382</v>
+        <v>358</v>
       </c>
       <c r="C182" s="9">
         <v>1059</v>
@@ -46636,10 +46636,10 @@
     </row>
     <row r="183" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="C183" s="9">
         <v>1305</v>
@@ -46718,10 +46718,10 @@
     </row>
     <row r="184" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
-        <v>385</v>
+        <v>361</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="C184" s="9">
         <v>1146</v>
@@ -46800,10 +46800,10 @@
     </row>
     <row r="185" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="C185" s="9">
         <v>2286</v>
@@ -46882,10 +46882,10 @@
     </row>
     <row r="186" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C186" s="9">
         <v>2127</v>
@@ -46964,10 +46964,10 @@
     </row>
     <row r="187" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A187" s="8" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="C187" s="9">
         <v>1968</v>
@@ -47046,10 +47046,10 @@
     </row>
     <row r="188" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A188" s="8" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="C188" s="9">
         <v>1740</v>
@@ -47128,10 +47128,10 @@
     </row>
     <row r="189" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="C189" s="9">
         <v>2451</v>
@@ -47210,10 +47210,10 @@
     </row>
     <row r="190" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="C190" s="9">
         <v>2418</v>
@@ -47292,10 +47292,10 @@
     </row>
     <row r="191" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>697</v>
+        <v>673</v>
       </c>
       <c r="C191" s="9">
         <v>3027</v>
@@ -47374,10 +47374,10 @@
     </row>
     <row r="192" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="C192" s="9">
         <v>2310</v>
@@ -47456,10 +47456,10 @@
     </row>
     <row r="193" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="C193" s="9">
         <v>1977</v>
@@ -47538,10 +47538,10 @@
     </row>
     <row r="194" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A194" s="8" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="C194" s="9">
         <v>975</v>
@@ -47620,10 +47620,10 @@
     </row>
     <row r="195" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="C195" s="9">
         <v>1479</v>
@@ -47702,10 +47702,10 @@
     </row>
     <row r="196" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="C196" s="9">
         <v>903</v>
@@ -47784,10 +47784,10 @@
     </row>
     <row r="197" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="C197" s="9">
         <v>1149</v>
@@ -47866,10 +47866,10 @@
     </row>
     <row r="198" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A198" s="8" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="C198" s="9">
         <v>1836</v>
@@ -47948,10 +47948,10 @@
     </row>
     <row r="199" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A199" s="8" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="C199" s="9">
         <v>1128</v>
@@ -48030,10 +48030,10 @@
     </row>
     <row r="200" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A200" s="8" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="C200" s="9">
         <v>1563</v>
@@ -48112,10 +48112,10 @@
     </row>
     <row r="201" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A201" s="8" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="C201" s="9">
         <v>1659</v>
@@ -48194,10 +48194,10 @@
     </row>
     <row r="202" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="C202" s="9">
         <v>1854</v>
@@ -48276,10 +48276,10 @@
     </row>
     <row r="203" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="C203" s="9">
         <v>1479</v>
@@ -48358,10 +48358,10 @@
     </row>
     <row r="204" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="C204" s="9">
         <v>2202</v>
@@ -48440,10 +48440,10 @@
     </row>
     <row r="205" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="C205" s="9">
         <v>3054</v>
@@ -48522,10 +48522,10 @@
     </row>
     <row r="206" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="C206" s="9">
         <v>4197</v>
@@ -48604,10 +48604,10 @@
     </row>
     <row r="207" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A207" s="8" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="C207" s="9">
         <v>1374</v>
@@ -48686,10 +48686,10 @@
     </row>
     <row r="208" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C208" s="9">
         <v>1437</v>
@@ -48768,10 +48768,10 @@
     </row>
     <row r="209" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="C209" s="9">
         <v>1386</v>
@@ -48850,10 +48850,10 @@
     </row>
     <row r="210" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="C210" s="9">
         <v>1194</v>
@@ -48932,10 +48932,10 @@
     </row>
     <row r="211" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A211" s="8" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="C211" s="9">
         <v>2955</v>
@@ -49014,10 +49014,10 @@
     </row>
     <row r="212" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A212" s="8" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="C212" s="9">
         <v>2811</v>
@@ -49096,10 +49096,10 @@
     </row>
     <row r="213" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A213" s="8" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="C213" s="9">
         <v>1110</v>
@@ -49178,10 +49178,10 @@
     </row>
     <row r="214" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A214" s="8" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C214" s="9">
         <v>1452</v>
@@ -49260,10 +49260,10 @@
     </row>
     <row r="215" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="C215" s="9">
         <v>1266</v>
@@ -49342,10 +49342,10 @@
     </row>
     <row r="216" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="C216" s="9">
         <v>1380</v>
@@ -49424,10 +49424,10 @@
     </row>
     <row r="217" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="C217" s="9">
         <v>1089</v>
@@ -49506,10 +49506,10 @@
     </row>
     <row r="218" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="C218" s="9">
         <v>1287</v>
@@ -49588,10 +49588,10 @@
     </row>
     <row r="219" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="C219" s="9">
         <v>864</v>
@@ -49670,10 +49670,10 @@
     </row>
     <row r="220" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A220" s="8" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="C220" s="9">
         <v>891</v>
@@ -49752,10 +49752,10 @@
     </row>
     <row r="221" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="C221" s="9">
         <v>870</v>
@@ -49834,10 +49834,10 @@
     </row>
     <row r="222" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C222" s="9">
         <v>951</v>
@@ -49916,10 +49916,10 @@
     </row>
     <row r="223" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A223" s="8" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C223" s="9">
         <v>1197</v>
@@ -49998,10 +49998,10 @@
     </row>
     <row r="224" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C224" s="9">
         <v>1068</v>
@@ -50080,10 +50080,10 @@
     </row>
     <row r="225" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C225" s="9">
         <v>1404</v>
@@ -50162,10 +50162,10 @@
     </row>
     <row r="226" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="C226" s="9">
         <v>1248</v>
@@ -50244,10 +50244,10 @@
     </row>
     <row r="227" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A227" s="8" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C227" s="9">
         <v>1656</v>
@@ -50326,10 +50326,10 @@
     </row>
     <row r="228" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A228" s="8" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C228" s="9">
         <v>1377</v>
@@ -50408,10 +50408,10 @@
     </row>
     <row r="229" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A229" s="8" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C229" s="9">
         <v>1572</v>
@@ -50490,10 +50490,10 @@
     </row>
     <row r="230" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C230" s="9">
         <v>1584</v>
@@ -50572,10 +50572,10 @@
     </row>
     <row r="231" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C231" s="9">
         <v>1383</v>
@@ -50654,10 +50654,10 @@
     </row>
     <row r="232" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="C232" s="9">
         <v>1800</v>
@@ -50736,10 +50736,10 @@
     </row>
     <row r="233" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="C233" s="9">
         <v>2025</v>
@@ -50818,10 +50818,10 @@
     </row>
     <row r="234" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="C234" s="9">
         <v>1491</v>
@@ -50900,10 +50900,10 @@
     </row>
     <row r="235" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A235" s="8" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="C235" s="9">
         <v>1182</v>
@@ -50982,10 +50982,10 @@
     </row>
     <row r="236" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="C236" s="9">
         <v>1086</v>
@@ -51064,10 +51064,10 @@
     </row>
     <row r="237" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>491</v>
+        <v>467</v>
       </c>
       <c r="C237" s="9">
         <v>1275</v>
@@ -51146,10 +51146,10 @@
     </row>
     <row r="238" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A238" s="8" t="s">
-        <v>492</v>
+        <v>468</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="C238" s="9">
         <v>1680</v>
@@ -51228,10 +51228,10 @@
     </row>
     <row r="239" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
       <c r="C239" s="9">
         <v>1980</v>
@@ -51310,10 +51310,10 @@
     </row>
     <row r="240" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A240" s="8" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="C240" s="9">
         <v>2088</v>
@@ -51392,10 +51392,10 @@
     </row>
     <row r="241" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="C241" s="9">
         <v>1905</v>
@@ -51474,10 +51474,10 @@
     </row>
     <row r="242" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A242" s="8" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="C242" s="9">
         <v>1779</v>
@@ -51556,10 +51556,10 @@
     </row>
     <row r="243" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A243" s="8" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="C243" s="9">
         <v>1476</v>
@@ -51638,10 +51638,10 @@
     </row>
     <row r="244" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A244" s="8" t="s">
-        <v>504</v>
+        <v>480</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>505</v>
+        <v>481</v>
       </c>
       <c r="C244" s="9">
         <v>1362</v>
@@ -51720,10 +51720,10 @@
     </row>
     <row r="245" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="B245" s="7" t="s">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="C245" s="9">
         <v>1659</v>
@@ -51802,10 +51802,10 @@
     </row>
     <row r="246" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>509</v>
+        <v>485</v>
       </c>
       <c r="C246" s="9">
         <v>1026</v>
@@ -51884,10 +51884,10 @@
     </row>
     <row r="247" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
-        <v>510</v>
+        <v>486</v>
       </c>
       <c r="B247" s="7" t="s">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="C247" s="9">
         <v>1374</v>
@@ -51966,10 +51966,10 @@
     </row>
     <row r="248" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
-        <v>512</v>
+        <v>488</v>
       </c>
       <c r="B248" s="7" t="s">
-        <v>513</v>
+        <v>489</v>
       </c>
       <c r="C248" s="9">
         <v>1137</v>
@@ -52048,10 +52048,10 @@
     </row>
     <row r="249" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
-        <v>514</v>
+        <v>490</v>
       </c>
       <c r="B249" s="7" t="s">
-        <v>515</v>
+        <v>491</v>
       </c>
       <c r="C249" s="9">
         <v>1440</v>
@@ -52130,10 +52130,10 @@
     </row>
     <row r="250" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A250" s="8" t="s">
-        <v>516</v>
+        <v>492</v>
       </c>
       <c r="B250" s="7" t="s">
-        <v>517</v>
+        <v>493</v>
       </c>
       <c r="C250" s="9">
         <v>1479</v>
@@ -52212,10 +52212,10 @@
     </row>
     <row r="251" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="B251" s="7" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
       <c r="C251" s="9">
         <v>1590</v>
@@ -52294,10 +52294,10 @@
     </row>
     <row r="252" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
-        <v>520</v>
+        <v>496</v>
       </c>
       <c r="B252" s="7" t="s">
-        <v>521</v>
+        <v>497</v>
       </c>
       <c r="C252" s="9">
         <v>1746</v>
@@ -52376,10 +52376,10 @@
     </row>
     <row r="253" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A253" s="8" t="s">
-        <v>522</v>
+        <v>498</v>
       </c>
       <c r="B253" s="7" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="C253" s="9">
         <v>1101</v>
@@ -52458,10 +52458,10 @@
     </row>
     <row r="254" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A254" s="8" t="s">
-        <v>524</v>
+        <v>500</v>
       </c>
       <c r="B254" s="7" t="s">
-        <v>525</v>
+        <v>501</v>
       </c>
       <c r="C254" s="9">
         <v>1089</v>
@@ -52540,10 +52540,10 @@
     </row>
     <row r="255" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A255" s="8" t="s">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="B255" s="7" t="s">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="C255" s="9">
         <v>1587</v>
@@ -52622,10 +52622,10 @@
     </row>
     <row r="256" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A256" s="8" t="s">
-        <v>528</v>
+        <v>504</v>
       </c>
       <c r="B256" s="7" t="s">
-        <v>529</v>
+        <v>505</v>
       </c>
       <c r="C256" s="9">
         <v>1080</v>
@@ -52704,10 +52704,10 @@
     </row>
     <row r="257" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A257" s="8" t="s">
-        <v>530</v>
+        <v>506</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>531</v>
+        <v>507</v>
       </c>
       <c r="C257" s="9">
         <v>1272</v>
@@ -52786,10 +52786,10 @@
     </row>
     <row r="258" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A258" s="8" t="s">
-        <v>532</v>
+        <v>508</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>533</v>
+        <v>509</v>
       </c>
       <c r="C258" s="9">
         <v>1242</v>
@@ -52868,10 +52868,10 @@
     </row>
     <row r="259" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A259" s="8" t="s">
-        <v>534</v>
+        <v>510</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="C259" s="9">
         <v>1710</v>
@@ -52950,10 +52950,10 @@
     </row>
     <row r="260" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A260" s="8" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>537</v>
+        <v>513</v>
       </c>
       <c r="C260" s="9">
         <v>978</v>
@@ -53032,10 +53032,10 @@
     </row>
     <row r="261" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A261" s="8" t="s">
-        <v>538</v>
+        <v>514</v>
       </c>
       <c r="B261" s="7" t="s">
-        <v>539</v>
+        <v>515</v>
       </c>
       <c r="C261" s="9">
         <v>1275</v>
@@ -53114,10 +53114,10 @@
     </row>
     <row r="262" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A262" s="8" t="s">
-        <v>540</v>
+        <v>516</v>
       </c>
       <c r="B262" s="7" t="s">
-        <v>541</v>
+        <v>517</v>
       </c>
       <c r="C262" s="9">
         <v>1137</v>
@@ -53196,10 +53196,10 @@
     </row>
     <row r="263" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A263" s="8" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="B263" s="7" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="C263" s="9">
         <v>1446</v>
@@ -53278,10 +53278,10 @@
     </row>
     <row r="264" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A264" s="8" t="s">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>545</v>
+        <v>521</v>
       </c>
       <c r="C264" s="9">
         <v>1044</v>
@@ -53360,10 +53360,10 @@
     </row>
     <row r="265" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A265" s="8" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>547</v>
+        <v>523</v>
       </c>
       <c r="C265" s="9">
         <v>1038</v>
@@ -53442,10 +53442,10 @@
     </row>
     <row r="266" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A266" s="8" t="s">
-        <v>548</v>
+        <v>524</v>
       </c>
       <c r="B266" s="7" t="s">
-        <v>549</v>
+        <v>525</v>
       </c>
       <c r="C266" s="9">
         <v>1344</v>
@@ -53524,10 +53524,10 @@
     </row>
     <row r="267" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A267" s="8" t="s">
-        <v>550</v>
+        <v>526</v>
       </c>
       <c r="B267" s="7" t="s">
-        <v>698</v>
+        <v>674</v>
       </c>
       <c r="C267" s="9">
         <v>1299</v>
@@ -53606,10 +53606,10 @@
     </row>
     <row r="268" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A268" s="8" t="s">
-        <v>551</v>
+        <v>527</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>552</v>
+        <v>528</v>
       </c>
       <c r="C268" s="9">
         <v>1005</v>
@@ -53688,10 +53688,10 @@
     </row>
     <row r="269" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A269" s="8" t="s">
-        <v>553</v>
+        <v>529</v>
       </c>
       <c r="B269" s="7" t="s">
-        <v>554</v>
+        <v>530</v>
       </c>
       <c r="C269" s="9">
         <v>1461</v>
@@ -53770,10 +53770,10 @@
     </row>
     <row r="270" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A270" s="8" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>699</v>
+        <v>675</v>
       </c>
       <c r="C270" s="9">
         <v>1389</v>
@@ -53852,10 +53852,10 @@
     </row>
     <row r="271" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A271" s="8" t="s">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="C271" s="9">
         <v>1533</v>
@@ -53934,10 +53934,10 @@
     </row>
     <row r="272" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A272" s="8" t="s">
-        <v>558</v>
+        <v>534</v>
       </c>
       <c r="B272" s="7" t="s">
-        <v>559</v>
+        <v>535</v>
       </c>
       <c r="C272" s="9">
         <v>1506</v>
@@ -54016,10 +54016,10 @@
     </row>
     <row r="273" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A273" s="8" t="s">
-        <v>560</v>
+        <v>536</v>
       </c>
       <c r="B273" s="7" t="s">
-        <v>561</v>
+        <v>537</v>
       </c>
       <c r="C273" s="9">
         <v>1602</v>
@@ -54098,10 +54098,10 @@
     </row>
     <row r="274" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A274" s="8" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
       <c r="B274" s="7" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
       <c r="C274" s="9">
         <v>1716</v>
@@ -54180,10 +54180,10 @@
     </row>
     <row r="275" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A275" s="8" t="s">
-        <v>564</v>
+        <v>540</v>
       </c>
       <c r="B275" s="7" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
       <c r="C275" s="9">
         <v>2196</v>
@@ -54262,10 +54262,10 @@
     </row>
     <row r="276" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A276" s="8" t="s">
-        <v>566</v>
+        <v>542</v>
       </c>
       <c r="B276" s="7" t="s">
-        <v>567</v>
+        <v>543</v>
       </c>
       <c r="C276" s="9">
         <v>1569</v>
@@ -54344,10 +54344,10 @@
     </row>
     <row r="277" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A277" s="8" t="s">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="B277" s="7" t="s">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="C277" s="9">
         <v>1674</v>
@@ -54426,10 +54426,10 @@
     </row>
     <row r="278" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A278" s="8" t="s">
-        <v>570</v>
+        <v>546</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="C278" s="9">
         <v>1701</v>
@@ -54508,10 +54508,10 @@
     </row>
     <row r="279" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A279" s="8" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>572</v>
+        <v>548</v>
       </c>
       <c r="C279" s="9">
         <v>2160</v>
@@ -54590,10 +54590,10 @@
     </row>
     <row r="280" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A280" s="8" t="s">
-        <v>573</v>
+        <v>549</v>
       </c>
       <c r="B280" s="7" t="s">
-        <v>574</v>
+        <v>550</v>
       </c>
       <c r="C280" s="9">
         <v>1125</v>
@@ -54672,10 +54672,10 @@
     </row>
     <row r="281" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A281" s="8" t="s">
-        <v>575</v>
+        <v>551</v>
       </c>
       <c r="B281" s="7" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="C281" s="9">
         <v>1260</v>
@@ -54754,10 +54754,10 @@
     </row>
     <row r="282" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A282" s="8" t="s">
-        <v>577</v>
+        <v>553</v>
       </c>
       <c r="B282" s="7" t="s">
-        <v>701</v>
+        <v>677</v>
       </c>
       <c r="C282" s="9">
         <v>1989</v>
@@ -54836,10 +54836,10 @@
     </row>
     <row r="283" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A283" s="8" t="s">
-        <v>578</v>
+        <v>554</v>
       </c>
       <c r="B283" s="7" t="s">
-        <v>579</v>
+        <v>555</v>
       </c>
       <c r="C283" s="9">
         <v>2073</v>
@@ -54918,10 +54918,10 @@
     </row>
     <row r="284" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A284" s="8" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="B284" s="7" t="s">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="C284" s="9">
         <v>1866</v>
@@ -55000,10 +55000,10 @@
     </row>
     <row r="285" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A285" s="8" t="s">
-        <v>582</v>
+        <v>558</v>
       </c>
       <c r="B285" s="7" t="s">
-        <v>583</v>
+        <v>559</v>
       </c>
       <c r="C285" s="9">
         <v>1935</v>
@@ -55082,10 +55082,10 @@
     </row>
     <row r="286" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A286" s="8" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="B286" s="7" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="C286" s="9">
         <v>1518</v>
@@ -55164,10 +55164,10 @@
     </row>
     <row r="287" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A287" s="8" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="B287" s="7" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="C287" s="9">
         <v>2235</v>
@@ -55246,10 +55246,10 @@
     </row>
     <row r="288" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A288" s="8" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B288" s="7" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="C288" s="9">
         <v>1524</v>
@@ -55328,10 +55328,10 @@
     </row>
     <row r="289" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A289" s="8" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="B289" s="7" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="C289" s="9">
         <v>1785</v>
@@ -55410,10 +55410,10 @@
     </row>
     <row r="290" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A290" s="8" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="B290" s="7" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="C290" s="9">
         <v>1590</v>
@@ -55492,10 +55492,10 @@
     </row>
     <row r="291" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A291" s="8" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="B291" s="7" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="C291" s="9">
         <v>1209</v>
@@ -55574,10 +55574,10 @@
     </row>
     <row r="292" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A292" s="8" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
       <c r="B292" s="7" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="C292" s="9">
         <v>1614</v>
@@ -55656,10 +55656,10 @@
     </row>
     <row r="293" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A293" s="8" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="B293" s="7" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C293" s="9">
         <v>1635</v>
@@ -55738,10 +55738,10 @@
     </row>
     <row r="294" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A294" s="8" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B294" s="7" t="s">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="C294" s="9">
         <v>1134</v>
@@ -55820,10 +55820,10 @@
     </row>
     <row r="295" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A295" s="8" t="s">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="B295" s="7" t="s">
-        <v>603</v>
+        <v>579</v>
       </c>
       <c r="C295" s="9">
         <v>957</v>
@@ -55902,10 +55902,10 @@
     </row>
     <row r="296" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A296" s="8" t="s">
-        <v>604</v>
+        <v>580</v>
       </c>
       <c r="B296" s="7" t="s">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="C296" s="9">
         <v>1041</v>
@@ -55984,10 +55984,10 @@
     </row>
     <row r="297" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A297" s="8" t="s">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="B297" s="7" t="s">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="C297" s="9">
         <v>1017</v>
@@ -56066,10 +56066,10 @@
     </row>
     <row r="298" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A298" s="8" t="s">
-        <v>608</v>
+        <v>584</v>
       </c>
       <c r="B298" s="7" t="s">
-        <v>609</v>
+        <v>585</v>
       </c>
       <c r="C298" s="9">
         <v>990</v>
@@ -56148,10 +56148,10 @@
     </row>
     <row r="299" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A299" s="8" t="s">
-        <v>610</v>
+        <v>586</v>
       </c>
       <c r="B299" s="7" t="s">
-        <v>611</v>
+        <v>587</v>
       </c>
       <c r="C299" s="9">
         <v>1665</v>
@@ -56230,10 +56230,10 @@
     </row>
     <row r="300" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A300" s="8" t="s">
-        <v>612</v>
+        <v>588</v>
       </c>
       <c r="B300" s="7" t="s">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="C300" s="9">
         <v>1020</v>
@@ -56312,10 +56312,10 @@
     </row>
     <row r="301" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A301" s="8" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="B301" s="7" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C301" s="9">
         <v>954</v>
@@ -56394,10 +56394,10 @@
     </row>
     <row r="302" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A302" s="8" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B302" s="7" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C302" s="9">
         <v>966</v>
@@ -56476,10 +56476,10 @@
     </row>
     <row r="303" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A303" s="8" t="s">
-        <v>614</v>
+        <v>590</v>
       </c>
       <c r="B303" s="7" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="C303" s="9">
         <v>978</v>
@@ -56558,10 +56558,10 @@
     </row>
     <row r="304" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A304" s="8" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="B304" s="7" t="s">
-        <v>617</v>
+        <v>593</v>
       </c>
       <c r="C304" s="9">
         <v>987</v>
@@ -56640,10 +56640,10 @@
     </row>
     <row r="305" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A305" s="8" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="B305" s="7" t="s">
-        <v>619</v>
+        <v>595</v>
       </c>
       <c r="C305" s="9">
         <v>996</v>
@@ -56722,10 +56722,10 @@
     </row>
     <row r="306" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A306" s="8" t="s">
-        <v>620</v>
+        <v>596</v>
       </c>
       <c r="B306" s="7" t="s">
-        <v>621</v>
+        <v>597</v>
       </c>
       <c r="C306" s="9">
         <v>1002</v>
@@ -56804,10 +56804,10 @@
     </row>
     <row r="307" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A307" s="8" t="s">
-        <v>622</v>
+        <v>598</v>
       </c>
       <c r="B307" s="7" t="s">
-        <v>623</v>
+        <v>599</v>
       </c>
       <c r="C307" s="9">
         <v>1011</v>
@@ -56886,10 +56886,10 @@
     </row>
     <row r="308" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A308" s="8" t="s">
-        <v>624</v>
+        <v>600</v>
       </c>
       <c r="B308" s="7" t="s">
-        <v>625</v>
+        <v>601</v>
       </c>
       <c r="C308" s="9">
         <v>1017</v>
@@ -56968,10 +56968,10 @@
     </row>
     <row r="309" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A309" s="8" t="s">
-        <v>626</v>
+        <v>602</v>
       </c>
       <c r="B309" s="7" t="s">
-        <v>627</v>
+        <v>603</v>
       </c>
       <c r="C309" s="9">
         <v>1020</v>
@@ -57050,10 +57050,10 @@
     </row>
     <row r="310" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A310" s="8" t="s">
-        <v>628</v>
+        <v>604</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>629</v>
+        <v>605</v>
       </c>
       <c r="C310" s="9">
         <v>1023</v>
@@ -57132,10 +57132,10 @@
     </row>
     <row r="311" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A311" s="8" t="s">
-        <v>630</v>
+        <v>606</v>
       </c>
       <c r="B311" s="7" t="s">
-        <v>631</v>
+        <v>607</v>
       </c>
       <c r="C311" s="9">
         <v>1029</v>
@@ -57214,10 +57214,10 @@
     </row>
     <row r="312" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A312" s="8" t="s">
-        <v>632</v>
+        <v>608</v>
       </c>
       <c r="B312" s="7" t="s">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="C312" s="9">
         <v>1032</v>
@@ -57296,10 +57296,10 @@
     </row>
     <row r="313" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A313" s="8" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="B313" s="7" t="s">
-        <v>635</v>
+        <v>611</v>
       </c>
       <c r="C313" s="9">
         <v>1038</v>
@@ -57378,10 +57378,10 @@
     </row>
     <row r="314" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A314" s="8" t="s">
-        <v>636</v>
+        <v>612</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>637</v>
+        <v>613</v>
       </c>
       <c r="C314" s="9">
         <v>1041</v>
@@ -57460,10 +57460,10 @@
     </row>
     <row r="315" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A315" s="8" t="s">
-        <v>638</v>
+        <v>614</v>
       </c>
       <c r="B315" s="7" t="s">
-        <v>639</v>
+        <v>615</v>
       </c>
       <c r="C315" s="9">
         <v>1047</v>
@@ -57542,10 +57542,10 @@
     </row>
     <row r="316" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A316" s="8" t="s">
-        <v>640</v>
+        <v>616</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="C316" s="9">
         <v>1053</v>
@@ -57624,10 +57624,10 @@
     </row>
     <row r="317" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A317" s="8" t="s">
-        <v>642</v>
+        <v>618</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="C317" s="9">
         <v>1062</v>
@@ -57706,10 +57706,10 @@
     </row>
     <row r="318" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A318" s="8" t="s">
-        <v>644</v>
+        <v>620</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>645</v>
+        <v>621</v>
       </c>
       <c r="C318" s="9">
         <v>1074</v>
@@ -57788,10 +57788,10 @@
     </row>
     <row r="319" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A319" s="8" t="s">
-        <v>646</v>
+        <v>622</v>
       </c>
       <c r="B319" s="7" t="s">
-        <v>647</v>
+        <v>623</v>
       </c>
       <c r="C319" s="9">
         <v>1089</v>
@@ -57870,10 +57870,10 @@
     </row>
     <row r="320" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A320" s="8" t="s">
-        <v>648</v>
+        <v>624</v>
       </c>
       <c r="B320" s="7" t="s">
-        <v>649</v>
+        <v>625</v>
       </c>
       <c r="C320" s="9">
         <v>1107</v>
@@ -57952,10 +57952,10 @@
     </row>
     <row r="321" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A321" s="8" t="s">
-        <v>650</v>
+        <v>626</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>651</v>
+        <v>627</v>
       </c>
       <c r="C321" s="9">
         <v>1122</v>
@@ -58034,10 +58034,10 @@
     </row>
     <row r="322" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A322" s="8" t="s">
-        <v>652</v>
+        <v>628</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>653</v>
+        <v>629</v>
       </c>
       <c r="C322" s="9">
         <v>1143</v>
@@ -58116,10 +58116,10 @@
     </row>
     <row r="323" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A323" s="8" t="s">
-        <v>654</v>
+        <v>630</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>655</v>
+        <v>631</v>
       </c>
       <c r="C323" s="9">
         <v>1167</v>
@@ -58198,10 +58198,10 @@
     </row>
     <row r="324" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A324" s="8" t="s">
-        <v>656</v>
+        <v>632</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>657</v>
+        <v>633</v>
       </c>
       <c r="C324" s="9">
         <v>1197</v>
@@ -58280,10 +58280,10 @@
     </row>
     <row r="325" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A325" s="8" t="s">
-        <v>658</v>
+        <v>634</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="C325" s="9">
         <v>1233</v>
@@ -58362,10 +58362,10 @@
     </row>
     <row r="326" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A326" s="8" t="s">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>661</v>
+        <v>637</v>
       </c>
       <c r="C326" s="9">
         <v>1263</v>
@@ -58444,10 +58444,10 @@
     </row>
     <row r="327" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A327" s="8" t="s">
-        <v>662</v>
+        <v>638</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="C327" s="9">
         <v>1293</v>
@@ -58526,10 +58526,10 @@
     </row>
     <row r="328" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A328" s="8" t="s">
-        <v>664</v>
+        <v>640</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>665</v>
+        <v>641</v>
       </c>
       <c r="C328" s="9">
         <v>1317</v>
@@ -58608,10 +58608,10 @@
     </row>
     <row r="329" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A329" s="8" t="s">
-        <v>666</v>
+        <v>642</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="C329" s="9">
         <v>1341</v>
@@ -58690,10 +58690,10 @@
     </row>
     <row r="330" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A330" s="8" t="s">
-        <v>668</v>
+        <v>644</v>
       </c>
       <c r="B330" s="7" t="s">
-        <v>669</v>
+        <v>645</v>
       </c>
       <c r="C330" s="9">
         <v>1365</v>
@@ -58772,10 +58772,10 @@
     </row>
     <row r="331" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A331" s="8" t="s">
-        <v>670</v>
+        <v>646</v>
       </c>
       <c r="B331" s="7" t="s">
-        <v>671</v>
+        <v>647</v>
       </c>
       <c r="C331" s="9">
         <v>1389</v>
@@ -58854,10 +58854,10 @@
     </row>
     <row r="332" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A332" s="8" t="s">
-        <v>672</v>
+        <v>648</v>
       </c>
       <c r="B332" s="7" t="s">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="C332" s="9">
         <v>1428</v>
@@ -58936,10 +58936,10 @@
     </row>
     <row r="333" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A333" s="8" t="s">
-        <v>674</v>
+        <v>650</v>
       </c>
       <c r="B333" s="7" t="s">
-        <v>675</v>
+        <v>651</v>
       </c>
       <c r="C333" s="9">
         <v>1482</v>
@@ -59018,10 +59018,10 @@
     </row>
     <row r="334" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A334" s="8" t="s">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="B334" s="7" t="s">
-        <v>677</v>
+        <v>653</v>
       </c>
       <c r="C334" s="9">
         <v>1539</v>
@@ -59100,10 +59100,10 @@
     </row>
     <row r="335" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A335" s="8" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="B335" s="7" t="s">
-        <v>679</v>
+        <v>655</v>
       </c>
       <c r="C335" s="9">
         <v>1611</v>
@@ -59182,10 +59182,10 @@
     </row>
     <row r="336" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A336" s="8" t="s">
-        <v>680</v>
+        <v>656</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>681</v>
+        <v>657</v>
       </c>
       <c r="C336" s="10">
         <v>1731</v>
@@ -59264,10 +59264,10 @@
     </row>
     <row r="337" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A337" s="8" t="s">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="B337" s="7" t="s">
-        <v>683</v>
+        <v>659</v>
       </c>
       <c r="C337" s="10">
         <v>1800</v>
@@ -59346,10 +59346,10 @@
     </row>
     <row r="338" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A338" s="8" t="s">
-        <v>684</v>
+        <v>660</v>
       </c>
       <c r="B338" s="7" t="s">
-        <v>685</v>
+        <v>661</v>
       </c>
       <c r="C338" s="9">
         <v>1902</v>
@@ -59428,10 +59428,10 @@
     </row>
     <row r="339" spans="1:28" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A339" s="8" t="s">
-        <v>686</v>
+        <v>662</v>
       </c>
       <c r="B339" s="7" t="s">
-        <v>687</v>
+        <v>663</v>
       </c>
       <c r="C339" s="9">
         <v>2157</v>
